--- a/output/adorsho poribar-test/book-output.xlsx
+++ b/output/adorsho poribar-test/book-output.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>প্রথম আদর্শ</t>
+          <t>নারী ও পুরুষের আদর্শ</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -502,53 +502,76 @@
           <t>&lt;div class="page-text"&gt;&lt;p&gt;নারী ও পুরুষ উভয়কেই যেমন সৃষ্টিকুলের মধ্যে বিশেষ সম্মানিত করে সৃষ্টি করা হয়েছে, তেমনি ইসলামের দৃষ্টিতে নারী-পুরুষের মধ্যে কিছু বিশেষ গুণের বাস্তবতা কামনা করা হয়েছে। এই গুণগুলোই তাদেরকে আদর্শবান হিসাবে তৈরি করতে পারে এবং একমাত্র এই আদর্শের অধিকারী নারী-পুরুষই ইসলামের দেওয়া মর্যাদা রক্ষা করতে পারে। নারী-পুরুষের পারস্পরিক সম্পর্ক ও তাদের পারিবারিক জীবনের বিবরণ পেশ করার পূর্বে তাদের বিশেষ বিশেষ কিছু গুণাবলি সংক্ষিপ্তভাবে পেশ করা হলো।&lt;/p&gt;
 &lt;p&gt;আল্লাহ তাআলা সূরা আহযাবের ৩৫-৩৬ নং আয়াতে আদর্শ নারী-পুরুষের জন্য ১২টি গুণ পেশ করেছেন। আমরা এইসব গুণাবলির সংক্ষিপ্ত বিবরণ দিয়ে বইয়ের প্রাথমিক আলোচনা আরম্ভ করলাম। আশা করি, নর-নারী সকল পাঠক এসব গুণাবলি অর্জন করে আল্লাহর সন্তুষ্টি লাভে ধন্য হবে। আল্লাহ তুমি কবুল কর-আমীন!&lt;/p&gt;
 &lt;ar&gt;إِنَّ الْمُسْلِمِينَ وَالْمُسْلِمَاتِ وَالْمُؤْمِنِينَ وَالْمُؤْمِنَاتِ وَالْقَانِتِينَ وَالْقَانِتَاتِ وَالصَّادِقِينَ وَالصَّادِقَاتِ وَالصَّابِرِينَ وَالصَّابِرَاتِ وَالْخَاشِعِينَ وَالْخَاشِعَاتِ وَالْمُتَصَدِّقِينَ وَالْمُتَصَدِّقَاتِ وَالصَّابِمِينَ وَالصَّابِمَاتِ وَالْحَافِظِينَ فُرُوجَهُمْ وَالْحَافِظَاتِ وَالذَّاكِرِينَ اللهَ كَثِيراً وَالذَّاكِرَاتِ أَعَدَّ اللهُ لَهُمُ مَغْفِرَةً وَأَجْراً عَظِيماً - وَمَا كَانَ لِمُؤْمِن وَلا مُؤْمِنَةٍ إِذَا قَضَى اللهُ وَرَسُولُهُ أَمْراً أَنْ يَكُونَ لَهُمُ الْخِيَرَةُ مِنْ أَمْرِهِمْ وَمَنْ يَعْصِ اللَّهَ وَرَسُولَهُ فَقَدْ ضَلَّ ضَلَالًا مُّبِيناً।&lt;/ar&gt;
-&lt;meaning&gt;অর্থ: 'আল্লাহর অনুগত পুরুষ ও স্ত্রীলোক, ঈমানদার পুরুষ ও স্ত্রীলোক, আল্লাহর দিকে মনোযোগকারী পুরুষ ও স্ত্রীলোক, সত্য ন্যায়বাদী পুরুষ ও স্ত্রীলোক, সত্যের পথে দৃঢ়তা প্রদর্শনকারী পুরুষ ও স্ত্রীলোক, আল্লাহর নিকট বিনীত-নম্র পুরুষ ও স্ত্রীলোক, দানশীল পুরুষ ও স্ত্রীলোক, ছিয়াম পালনকারী পুরুষ ও স্ত্রীলোক, লজ্জাস্থানের হেফাযতকারী পুরুষ ও স্ত্রীলোক, আল্লাহকে অধিক মাত্রায় স্মরণকারী পুরুষ ও স্ত্রীলোক, আল্লাহ এদের জন্য স্বীয় ক্ষমা ও&lt;/meaning&gt;
-&lt;meaning&gt;বিরাট পুরস্কার প্রস্তুত করে রেখেছেন। কোন ঈমানদার পুরুষ ও স্ত্রীলোকের জন্য আল্লাহ এবং তাঁর রাসূল যখন কোন বিষয়ে চূড়ান্তভাবে ফয়সালা করেন, তখন সে ব্যাপারে তার বিপরীত কিছু করার কারো কোন অধিকার নেই। আর যে ব্যক্তি আল্লাহ ও তাঁর রাসূলের নাফারমানী করে সে সুস্পষ্ট ভ্রান্ত' (আল-আহযাব, ৩৫-৩৬)।&lt;/meaning&gt;
-&lt;p&gt;উল্লিখিত আয়াতে আল্লাহ রব্বুল আলামীন এক জন আদর্শ নারী-পুরুষের জন্য এমন কিছু গুণাবলি বা বৈশিষ্ট্যের কথা উল্লেখ করেছেন। সেই গুণাবলি যদি কোন নারী-পুরুষের মাঝে বিদ্যমান থাকে, তাহলে তার জন্য মহাপুরস্কারের ঘোষণা দিয়েছেন। উল্লিখিত আয়াতে নারী-পুরুষের জন্য ১২টি শিক্ষণীয়, গ্রহণীয় ও অবশ্য পালনীয় আদর্শ রয়েছে। যা ধারাবাহিকভাবে উল্লেখ করা হলো।&lt;/p&gt;&lt;br&gt;&lt;div class="subheading"&gt;প্রথম আদর্শ&lt;/div&gt;&lt;br&gt;&lt;p&gt;মুসলিম পুরুষ ও মুসলিম স্ত্রীলোক। 'মুসলিম' শব্দের আভিধানিক অর্থ আত্মসমর্পণকারী। আর পারিভাষিক অর্থে আল্লাহ ও তাঁর রাসূল (ﷺ)-এর আঈন পালনকারী। আর পারিভাষিক অর্থ হচ্ছে, সুস্থতায়, অসুস্থতায়, সুখে, দুঃখে, সর্বময় ক্ষমতাধর আল্লাহ তাআলার নিকটে নতশীরে ইসলামের যাবতীয় বিধি-বিধান মেনে নেওয়া।&lt;/p&gt;
+&lt;meaning&gt;অর্থ: 'আল্লাহর অনুগত পুরুষ ও স্ত্রীলোক, ঈমানদার পুরুষ ও স্ত্রীলোক, আল্লাহর দিকে মনোযোগকারী পুরুষ ও স্ত্রীলোক, সত্য ন্যায়বাদী পুরুষ ও স্ত্রীলোক, সত্যের পথে দৃঢ়তা প্রদর্শনকারী পুরুষ ও স্ত্রীলোক, আল্লাহর নিকট বিনীত-নম্র পুরুষ ও স্ত্রীলোক, দানশীল পুরুষ ও স্ত্রীলোক, ছিয়াম পালনকারী পুরষ ও স্ত্রীলোক, লজ্জাস্থানের হেফাযতকারী পুরুষ ও স্ত্রীলোক, আল্লাহকে অধিক মাত্রায় স্মরণকারী পুরুষ ও স্ত্রীলোক, আল্লাহ এদের জন্য স্বীয় ক্ষমা ও বিরাট পুরস্কার প্রস্তুত করে রেখেছেন। কোন ঈমানদার পুরুষ ও স্ত্রীলোকের জন্য আল্লাহ এবং তাঁর রাসূল যখন কোন বিষয়ে চূড়ান্তভাবে ফয়সালা করেন, তখন সে ব্যাপারে তার বিপরীত কিছু করার কারো কোন অধিকার নেই। আর যে ব্যক্তি আল্লাহ ও তাঁর রাসূলের নাফারমানী করে সে সুস্পষ্ট ভ্রান্ত' (আল-আহযাব, ৩৫-৩৬)।&lt;/meaning&gt;
+&lt;p&gt;উল্লিখিত আয়াতে আল্লাহ রব্বুল আলামীন এক জন আদর্শ নারী-পুরুষের জন্য এমন কিছু গুণাবলি বা বৈশিষ্ট্যের কথা উল্লেখ করেছেন। সেই গুণাবলি যদি কোন নারী-পুরুষের মাঝে বিদ্যমান থাকে, তাহলে তার জন্য মহাপুরস্কারের ঘোষণা দিয়েছেন। উল্লিখিত আয়াতে নারী-পুরুষের জন্য ১২টি শিক্ষণীয়, গ্রহণীয় ও অবশ্য পালনীয় আদর্শ রয়েছে। যা ধারাবাহিকভাবে উল্লেখ করা হলো।&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>নারী ও পুরুষের আদর্শ</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>প্রথম আদর্শ</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>&lt;div class="page-text"&gt;&lt;p&gt;মুসলিম পুরুষ ও মুসলিম স্ত্রীলোক। 'মুসলিম' শব্দের আভিধানিক অর্থ আত্মসমর্পণকারী। আর পারিভাষিক অর্থে আল্লাহ ও তাঁর রাসূল (ﷺ)-এর আঈন পালনকারী। আর পারিভাষিক অর্থ হচ্ছে, সুস্থতায়, অসুস্থতায়, সুখে, দুঃখে, সর্বময় ক্ষমতাধর আল্লাহ তাআলার নিকটে নতশীরে ইসলামের যাবতীয় বিধি-বিধান মেনে নেওয়া।&lt;/p&gt;
 &lt;p&gt;এক জন আদর্শ মানুষ হওয়ার জন্য বা প্রকৃত মুসলিম হওয়ার জন্য রাসূলুল্লাহ (ﷺ) কিছু গুণাবলির কথা উল্লেখ করেছেন। যেমন রাসূলুল্লাহ (ﷺ)-এর বাণী-&lt;/p&gt;
 &lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو عَنِ النَّبِيَّ ﷺ قَالَ : ( الْمُسْلِمُ مَنْ سَلِمَ الْمُسْلِمُونَ مِنْ لِسَانِهِ وَيَدِهِ।&lt;/ar&gt;
 &lt;p&gt;আব্দুল্লাহ ইবনু আমর (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'পূর্ণ মুসলিম সে পুরুষ বা নারী, যার যবান ও হাত হতে অন্যান্য পুরুষ বা নারী নিরাপদে থাকে' (ছহীহ বুখারী, হা/১০,৬৪৮৪; ছহীহ মুসলিম, হা/১৭১; মিশকাত, হা/৬)।&lt;/p&gt;
-&lt;p&gt;হাদীছের অর্থ হচ্ছে শরীআতের হুকুম ব্যতীত যেকোনো মানুষকে যেকোনো রকমের কষ্ট দেওয়া ইসলাম বিরোধী কাজ। এতে মানুষ পূর্ণ মুসলিম থাকে না। অন্য বর্ণনায় রয়েছে, 'মুসলিম সে ব্যক্তি যে, নিজের জন্য যেটা কল্যাণকর মনে করে অন্যের জন্যও সেটা কল্যাণকর মনে করে' (তিরমিযী, হা/২৩০৫; ইবনু মাজাহ, হা/৪২১৭; মিশকাত, হা/৫১৭১)। মানুষকে কষ্ট দেওয়া সদাচরণ বিরোধী কাজ, যার পরিণাম জাহান্নাম।&lt;/p&gt;
+&lt;p&gt;হাদীছের অর্থ হচ্ছে শরীয়তের হুকুম ব্যতীত যেকোনো মানুষকে যেকোনো রকমের কষ্ট দেওয়া ইসলাম বিরোধী কাজ। এতে মানুষ পূর্ণ মুসলিম থাকে না। অন্য বর্ণনায় রয়েছে, 'মুসলিম সে ব্যক্তি যে, নিজের জন্য যেটা কল্যাণকর মনে করে অন্যের জন্যও সেটা কল্যাণকর মনে করে' (তিরমিযী, হা/২৩০৫; ইবনু মাজাহ, হা/৪২১৭; মিশকাত, হা/৫১৭১)। মানুষকে কষ্ট দেওয়া সদাচরণ বিরোধী কাজ, যার পরিণাম জাহান্নাম।&lt;/p&gt;
 &lt;ar&gt;عَنْ جُبَيْرِ بْنِ مُطْعِمٍ الله أَخْبَرَهُ أَنَّهُ سَمِعَ النَّبِيَّ ﷺ يَقُولُ : « لَا يَدْخُلُ الْجَنَّةَ قَاطِعُ»।&lt;/ar&gt;
 &lt;p&gt;জুবায়ের ইবনু মুত্বইম (রাঃ) বলেন, নবী (ﷺ) বলেছেন, 'পরস্পর সম্পর্ক ছিন্নকারী জান্নাতে প্রবেশ করবে না' (ছহীহ বুখারী, হা/৫৯৮৪; ছহীহ মুসলিম, হা/৬৬৮৫; মিশকাত, হা/৪৭০৫)। কেননা সম্পর্ক ছিন্ন করাই হচ্ছে আদর্শ বিনষ্ট করার মূল। প্রকৃত মুসলিম হিসাবে না থাকার পরিচায়ক। উল্লেখ্য যে, উল্লিখিত আয়াতে আল্লাহ রব্বুল আলামীন মুসলিম এবং মু'মিনকে পারস্পরিকভাবে উল্লেখ করেছেন।&lt;/p&gt;
 &lt;ar&gt;عَنْ سُفْيَانَ بْنِ عَبْدِ اللَّهِ الثَّقَفِيِّ الله قَالَ : قُلْتُ : يَا رَسُولَ اللَّهِ قُلْ لِي فِي الْإِسْلَامِ قَوْلًا لَا أَسْأَلُ عَنْهُ أَحَدًا بَعْدَكَ وَفِي حَدِيثِ أَبِي أُسَامَةَ : غَيْرَكَ - قَالَ : « قُلْ آمَنْتُ بِاللَّهِ فَاسْتَقِمْ »।&lt;/ar&gt;
 &lt;p&gt;সুফইয়ান ইবনু আব্দুল্লাহ আস-সাক্বাফী (রাঃ) হতে বর্ণিত। তিনি বলেন, আমি আরয করলাম, হে আল্লাহর রাসূল! আপনি আমাকে ইসলামের এমন একটি চূড়ান্ত কথা বলে দিন, যে সম্পর্কে আপনার পরে আমাকে আর কারও নিকট জিজ্ঞাসা করতে না হয় (অপর এক বর্ণনায় আছে, আপনি ছাড়া আমাকে আর কারও কাছে জিজ্ঞাসা করতে না হয়)। নবী (ﷺ) বললেন, 'তুমি বল, আমি আল্লাহর উপর ঈমান এনেছি; অতঃপর তুমি এ কথার উপরে দৃঢ় থাক' (ছহীহ মুসলিম, হা/১৬৮; মুসনাদে আহমাদ, হা/১৫৪৫৪; মিশকাত, হা/১৫)।&lt;/p&gt;
 &lt;ar&gt;عَنْ عُمَرَ بْنِ الْخَطَابِ قَالَ : بَيْنَمَا نَحْنُ عِنْدَ رَسُولِ اللَّهِ ﷺ ذَاتَ يَوْمٍ إِذْ طَلَعَ عَلَيْنَا رَجُلٌ شَدِيدُ بَيَاضِ الثَّيَابِ شَدِيدُ سَوَادِ الشَّعَرِ لَا يُرى عَلَيْهِ أَثَرُ السَّفَرِ وَلَا يَعْرِفُهُ مِنَّا أَحَدٌ حَتَّى جَلَسَ إِلَى النَّبِيِّ فَأَسْنَدَ رُكْبَتَيْهِ إِلَى رُكْبَتَيْهِ وَوَضَعَ كَفَّيْهِ عَلَى فَخِذَيْهِ وَقَالَ يَا مُحَمَّدُ أَخْبِرْنِي عَنِ الإِسْلامِ। فَقَالَ رَسُولُ اللهِ ﷺ : ( الإِسْلَامُ أَنْ تَشْهَدَ أَنْ لَا إِلَهَ إِلَّا اللَّهُ وَأَنَّ مُحَمَّدًا رَسُولُ اللَّهِ وَتُقِيمَ الصَّلاةَ وَتُؤْتِي الزَّكَاةَ وَتَصُومَ رَمَضَانَ وَتَحُجَّ الْبَيْتَ إِنِ اسْتَطَعْتَ إِلَيْهِ سَبِيلاً।&lt;/ar&gt;
-&lt;p&gt;উমার ইবনুল খাত্ত্বাব (রাঃ) হতে বর্ণিত। তিনি বলেন, একদা আমরা রাসূলুল্লাহ (ﷺ)-এর দরবারে উপস্থিত ছিলাম। এমন সময় জনৈক ব্যক্তি দরবারে আত্মপ্রকাশ করলেন। ধবধবে সাদা তাঁর পোশাক। চুল তাঁর কুচকুচে কালো। না ছিল তার মধ্যে সফর করে আসার কোন চিহ্ন, আর না আমাদের কেউ তাকে চিনতে পেরেছেন। তিনি এসেই নবী (ﷺ)-এর নিকট বসে পড়লেন। নবী (ﷺ)-এর হাঁটুর সাথে তাঁর হাঁটু মিলিয়ে দিলেন। তাঁর দুই হাত তাঁর দুই উরুর উপর রেখে বললেন, 'হে মুহাম্মাদ! আমাকে ইসলাম সম্পর্কে কিছু বলুন। অর্থাৎ ইসলাম কি? উত্তরে নবী (ﷺ) বললেন, 'ইসলাম হচ্ছে- তুমি সাক্ষ্য দিবে আল্লাহ ছাড়া আর কোন সত্য ইলাহ (উপাস্য) নেই, মুহাম্মাদ আল্লাহর রাসূল, ছালাত কায়েম করবে, যাকাত আদায় করবে, রমাযান মাসের ছিয়াম পালন করবে এবং বায়তুল্লাহর হজ্জ করবে যদি সেখানে যাওয়ার সামর্থ্য থাকে' (ছহীহ মুসলিম, হা/১০২; আবু দাউদ, হা/৪৬৯৫; মিশকাত, হা/২)।&lt;/p&gt;
+&lt;p&gt;উমর ইবনুল খাত্ত্বাব (রাঃ) হতে বর্ণিত। তিনি বলেন, একদা আমরা রাসূলুল্লাহ (ﷺ)-এর দরবারে উপস্থিত ছিলাম। এমন সময় জনৈক ব্যক্তি দরবারে আত্মপ্রকাশ করলেন। ধবধবে সাদা তাঁর পোশাক। চুল তাঁর কুচকুচে কালো। না ছিল তার মধ্যে সফর করে আসার কোন চিহ্ন, আর না আমাদের কেউ তাকে চিনতে পেরেছেন। তিনি এসেই নবী (ﷺ)-এর নিকট বসে পড়লেন। নবী (ﷺ)-এর হাঁটুর সাথে তাঁর হাঁটু মিলিয়ে দিলেন। তাঁর দুই হাত তাঁর দুই উরুর উপর রেখে বললেন, 'হে মুহাম্মাদ! আমাকে ইসলাম সম্পর্কে কিছু বলুন। অর্থাৎ ইসলাম কি? উত্তরে নবী (ﷺ) বললেন, 'ইসলাম হচ্ছে- তুমি সাক্ষ্য দিবে আল্লাহ ছাড়া আর কোন সত্য ইলাহ (উপাস্য) নেই, মুহাম্মাদ আল্লাহর রাসূল, ছালাত কায়েম করবে, যাকাত আদায় করবে, রমাযান মাসের ছিয়াম পালন করবে এবং বায়তুল্লাহর হজ্জ করবে যদি সেখানে যাওয়ার সামর্থ্য থাকে' (ছহীহ মুসলিম, হা/১০২; আবু দাউদ, হা/৪৬৯৫; মিশকাত, হা/২)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ اللهِ قَالَ : قَالَ رَسُولُ اللهِ ﷺ : لِلْمُؤْمِنِ عَلَى الْمُؤْمِنِ سِتُّ خِصَالٍ: يَعُودُهُ إِذَا مَرِضَ، وَيَشْهَدُهُ إِذَا مَاتَ، وَيُجِيبُهُ إِذَا دَعَاهُ، وَيُسَلِّمُ عَلَيْهِ إِذَا لَقِيَهُ، وَيُشَمِّتُهُ إِذَا عَطَسَ، وَيَنْصَحُ لَهُ إِذَا غَابَ أَوْ شَهِدَ»।&lt;/ar&gt;
-&lt;p&gt;আবু হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'এক জন মুসলিমের উপর অপর মুসলিমের ছয়টি হক্ক রয়েছে। ১. যখন সে রোগে আক্রান্ত হয় তখন তার সেবা-শুশ্রুষা করবে। ২. সে মৃত্যুবরণ করলে তার জানাযা ও কাফন-দাফনে উপস্থিত থাকবে। ৩. দাওয়াত করলে তা গ্রহণ করবে। ৪. সাক্ষাৎ হলে তাকে সালাম দিবে। ৫. হাঁচি দিলে (يَرْحَمُكَ اللهُ-অর্থাৎ 'আল্লাহ তাআলা তোমার প্রতি রহম করুন' এই দু'আ বলে) তার জওয়াব দিবে এবং ৬. উপস্থিত বা অনুপস্থিত সকল অবস্থায় তার জন্য কল্যাণ কামনা করবে' (তিরমিযী, হা/২৭৩৭; নাসাঈ, হা/১৯৩৮; মিশকাত, হা/৪৬৩০)।&lt;/p&gt;
-&lt;p&gt;উপরিউক্ত আলোচনায় একজন মুসলিমের যে বৈশিষ্ট্য গুলো থাকা জরুরী তা নিচে আলোচনা করা হলো। ১. ইসলামে প্রবেশ করার জন্য প্রথমেই আল্লাহ তাআলার প্রতি বিশ্বাস স্থাপন করা। মুহাম্মাদ (ﷺ)-কে তাঁর রাসূল বা নবী হিসাবে বিশ্বাস করা। ২. দিনে-রাতে পাঁচ ওয়াক্ত ছালাত আদায় করা। ৩. নিসাব পরিমান সম্পদ থাকলে যাকাত প্রদান করা। ৪. রমাযান মাসে ছিয়াম পালন করা। ৫. সামর্থ্য থাকলে হজ্জ করা। ৬. অপর মুসলিমকে কষ্ট না দেওয়া। ৭. আত্মীয়তার সম্পর্ক ছিন্ন না করা। ৮. কোনো মুসলিম ভাই রোগাক্রান্ত হলে তাকে দেখতে যাওয়া এবং তার সেবা-শুশ্রুষা করা। ৯. কোন মুসলিম মারা গেলে তার জানাযায় উপস্থিত থাকা। ১০. কোন মুসলিম দাওয়াত করলে তার দাওয়াতে সাড়া দেওয়া। ১১. পরস্পর সকল মুসলিমকে সাক্ষাতকালে সালাম দেওয়া। আমাদের দেশে সামাজিক একটি কুঅভ্যাস চালু হয়েছে তাহল, শুধু পরিচিত সম্মানীদেরকে সালাম দেয়। আর যারা সম্মানী তারাও মনে&lt;/p&gt;
-&lt;p&gt;করে যে, আমাদেরকে সালাম দিক যা সম্পূর্ণ হারাম। এটাই অনুসরণীয় যে, পরিচিত-অপরিচিত, ছোট-বড় সকলকে সালাম দিতে হবে। কেননা ঐ ব্যক্তি সর্ব উত্তম, যে আগে সালাম দেয়। ১২. কোন মুসলিম হাঁচি দিলে তার উত্তরে 'ইয়ারহামুকা-ল্লাহ' বলা, আর হাঁচি দাতার 'ইয়াহদীকুমু-ল্লাহ' বলা। ১৩. সর্ব অবস্থায় এক জন মুসলিম অপর মুসলিমের জন্য কল্যাণ কামনা করা এবং সুপরামর্শ দেওয়া। উপরোক্ত গুনাবলি যদি কারো মধ্যে না থাকে, তাহলে সে পূর্ণ মুসলিম নয় অতএব উপরিউক্ত গুণাবলি এক জন মুসলিমের মধ্যে থাকা জরুরী।&lt;/p&gt;&lt;br&gt;&lt;div class="subheading"&gt;দ্বিতীয় আদর্শ&lt;/div&gt;&lt;br&gt;&lt;p&gt;মু'মিন পুরুষ ও মু'মিন নারী। 'মু'মিন' শব্দের অর্থ হচ্ছে, ঈমানদার। পরিভাষায় ঈমান হচ্ছে, একনিষ্ঠভাবে আল্লাহকে একমাত্র উপাস্য হিসেবে বিশ্বাস করা, রাসূলগণকে আল্লাহ তাআলার প্রেরিত রাসূল হিসেবে বিশ্বাস করা, পবিত্র কুরআন ও পূর্ববর্তী কিতাবসমূহের প্রতি বিশ্বাস করা, ফেরেশতাগণের প্রতি বিশ্বাস করা, কিয়ামত দিবসের প্রতি বিশ্বাস করা, তাক্বদীরের ভাল-মন্দের প্রতি বিশ্বাস স্থাপন করা, যেমন আল্লাহ তাআলার বাণী,&lt;/p&gt;
+&lt;p&gt;আবু হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'এক জন মুসলিমের উপর অপর মুসলিমের ছয়টি হক্ক রয়েছে। ১. যখন সে রোগে আক্রান্ত হয় তখন তার সেবা-শুশ্রুষা করবে। ২. সে মৃত্যুবরণ করলে তার জানাযা ও কাফন-দাফনে উপস্থিত থাকবে। ৩. দাওয়াত করলে তা গ্রহণ করবে। ৪. সাক্ষাৎ হলে তাকে সালাম দিবে। ৫. হাঁচি দিলে (يَرْحَمُكَ اللهُ-অর্থাৎ 'আল্লাহ তাআলা তোমার প্রতি রহম করুন' এই দোয়া বলে) তার জওয়াব দিবে এবং ৬. উপস্থিত বা অনুপস্থিত সকল অবস্থায় তার জন্য কল্যাণ কামনা করবে' (তিরমিযী, হা/২৭৩৭; নাসাঈ, হা/১৯৩৮; মিশকাত, হা/৪৬৩০)।&lt;/p&gt;
+&lt;p&gt;উপরিউক্ত আলোচনায় একজন মুসলিমের যে বৈশিষ্ট্য গুলো থাকা জরুরী তা নিচে আলোচনা করা হলো।&lt;br&gt;১. ইসলামে প্রবেশ করার জন্য প্রথমেই আল্লাহ তাআলার প্রতি বিশ্বাস স্থাপন করা। মুহাম্মাদ (ﷺ)-কে তাঁর রাসূল বা নবী হিসাবে বিশ্বাস করা।&lt;br&gt;২. দিনে-রাতে পাঁচ ওয়াক্ত ছালাত আদায় করা।&lt;br&gt;৩. নিসাব পরিমান সম্পদ থাকলে যাকাত প্রদান করা।&lt;br&gt;৪. রমাযান মাসে ছিয়াম পালন করা।&lt;br&gt;৫. সামর্থ্য থাকলে হজ্জ করা।&lt;br&gt;৬. অপর মুসলিমকে কষ্ট না দেওয়া।&lt;br&gt;৭. আত্মীয়তার সম্পর্ক ছিন্ন না করা।&lt;br&gt;৮. কোনো মুসলিম ভাই রোগাক্রান্ত হলে তাকে দেখতে যাওয়া এবং তার সেবা-শুশ্রুষা করা।&lt;br&gt;৯. কোন মুসলিম মারা গেলে তার জানাযায় উপস্থিত থাকা।&lt;br&gt;১০. কোন মুসলিম দাওয়াত করলে তার দাওয়াতে সাড়া দেওয়া।&lt;br&gt;১১. পরস্পর সকল মুসলিমকে সাক্ষাতকালে সালাম দেওয়া। আমাদের দেশে সামাজিক একটি কুঅভ্যাস চালু হয়েছে তাহল, শুধু পরিচিত সম্মানীদেরকে সালাম দেয়। আর যারা সম্মানী তারাও মনে করে যে, আমাদেরকে সালাম দিক যা সম্পূর্ণ হারাম। এটাই অনুসরণীয় যে, পরিচিত-অপরিচিত, ছোট-বড় সকলকে সালাম দিতে হবে। কেননা ঐ ব্যক্তি সর্ব উত্তম, যে আগে সালাম দেয়।&lt;br&gt;১২. কোন মুসলিম হাঁচি দিলে তার উত্তরে 'ইয়ারহামুকা-ল্লাহ' বলা, আর হাঁচি দাতার 'ইয়াহদীকুমু-ল্লাহ' বলা।&lt;br&gt;১৩. সর্ব অবস্থায় এক জন মুসলিম অপর মুসলিমের জন্য কল্যাণ কামনা করা এবং সুপরামর্শ দেওয়া। উপরোক্ত গুনাবলি যদি কারো মধ্যে না থাকে, তাহলে সে পূর্ণ মুসলিম নয় অতএব উপরিউক্ত গুণাবলি এক জন মুসলিমের মধ্যে থাকা জরুরী।&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>নারী ও পুরুষের আদর্শ</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>দ্বিতীয় আদর্শ</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>&lt;div class="page-text"&gt;&lt;p&gt;মু'মিন পুরুষ ও মু'মিন নারী। 'মু'মিন' শব্দের অর্থ হচ্ছে, ঈমানদার। পরিভাষায় ঈমান হচ্ছে, একনিষ্ঠভাবে আল্লাহকে একমাত্র উপাস্য হিসেবে বিশ্বাস করা, রাসূলগণকে আল্লাহ তাআলার প্রেরিত রাসূল হিসেবে বিশ্বাস করা, পবিত্র কোরআন ও পূর্ববর্তী কিতাবসমূহের প্রতি বিশ্বাস করা, ফেরেশতাগণের প্রতি বিশ্বাস করা, কিয়ামত দিবসের প্রতি বিশ্বাস করা, তাক্বদীরের ভাল-মন্দের প্রতি বিশ্বাস স্থাপন করা, যেমন আল্লাহ তাআলার বাণী,&lt;/p&gt;
 &lt;ar&gt;آمَنَ الرَّسُولُ بِمَا أُنْزِلَ إِلَيْهِ مِنْ رَبِّهِ وَالْمُؤْمِنُونَ كُلٌّ آمَنَ بِاللَّهِ وَمَلَا بِكَتِهِ وَكُتُبِهِ وَرُسُلِهِ لَا نُفَرِّقُ بَيْنَ أَحَدٍ مِنْ رُسُلِهِ وَقَالُوا سَمِعْنَا وَأَطَعْنَا غُفْرَانَكَ رَبَّنَا وَإِلَيْكَ الْمَصِيرُ।&lt;/ar&gt;
 &lt;meaning&gt;অর্থ: রাসূল (ﷺ) তাঁর প্রতিপালকের পক্ষ থেকে তাঁর প্রতি যা অবতীর্ণ করা হয়েছে, তাতে ঈমান এনেছেন এবং মু'মিন গণও। তাঁরা সকলেই মহান আল্লাহ তাআলার উপর, তাঁর ফেরেশতাগণের উপর, তাঁর কিতাবসমূহের উপর এবং তাঁর রাসূলগণের উপর বিশ্বাস স্থাপন করেছে। তারা (মু'মিন গণ) বলে, আমরা রাসূলগণের র মধ্যেকোনো তারতম্য করি না এবং তারা এ কথাও বলে যে, আমরা শুনেছি এবং মেনে নিয়েছি' (আল-বাক্বারা, ২৮৫)।&lt;/meaning&gt;
 &lt;p&gt;অন্য এক আয়াতে আল্লাহ বলেন,&lt;/p&gt;
 &lt;ar&gt;قُلْ لَا أَمْلِكُ لِنَفْسِي نَفْعًا وَلَا ضَرًّا إِلَّا مَا شَاءَ اللَّهُ।&lt;/ar&gt;
 &lt;meaning&gt;অর্থ: বল, 'মহান আল্লাহ যা ইচ্ছা করেন, তাছাড়া আমার নিজের ভাল বা মন্দ করার কোন ক্ষমতা নেই' (আল-আরাফ, ১৮৮)।&lt;/meaning&gt;
-&lt;p&gt;উপরিউক্ত আয়াতদ্বয় দ্বারা বুঝা যায় যে, দৃশ্য-অদৃশ্য, ভাল-মন্দ, সব কিছু একমাত্র আল্লাহর অধীনে। তাঁর প্রতি বিশ্বাস স্থাপন করাই হচ্ছে প্রকৃত ঈমান। আর মু'মিনদের জন্য রয়েছে মহাপুরস্কার।&lt;/p&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>নারী ও পুরুষের আদর্শ</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>দ্বিতীয় আদর্শ</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>&lt;div class="page-text"&gt;&lt;p&gt;যেমন আল্লাহ তাআলার বাণী,&lt;/p&gt;
+&lt;p&gt;উপরিউক্ত আয়াতদ্বয় দ্বারা বুঝা যায় যে, দৃশ্য-অদৃশ্য, ভাল-মন্দ, সব কিছু একমাত্র আল্লাহর অধীনে। তাঁর প্রতি বিশ্বাস স্থাপন করাই হচ্ছে প্রকৃত ঈমান। আর মু'মিনদের জন্য রয়েছে মহাপুরস্কার।&lt;/p&gt;
+&lt;p&gt;যেমন আল্লাহ তাআলার বাণী,&lt;/p&gt;
 &lt;ar&gt;وَبَشِّرِ الَّذِينَ آمَنُوا وَعَمِلُوا الصَّالِحَاتِ أَنَّ لَهُمْ جَنَّاتٍ تَجْرِي مِنْ تَحْتِهَا الْأَنْهَارُ كُلَّمَا رُزِقُوا مِنْهَا مِنْ ثَمَرَةٍ رِزْقًا قَالُوا هَذَا الَّذِي رُزِقْنَا مِنْ قَبْلُ وَأُتُوا بِهِ مُتَشَابِهًا وَلَهُمْ فِيهَا أَزْوَاجٌ مُطَهَّرَةٌ وَهُمْ فِيهَا خَالِدُونَ.&lt;/ar&gt;
 &lt;meaning&gt;অর্থ: 'যারা (আল্লাহ তাআলার প্রতি) ঈমান আনে এবং সৎকর্ম করে, তাদের সুসংবাদ দাও যে, তাদের জন্য রয়েছে এমন জান্নাত, যার তলদেশ দিয়ে প্রবাহিত হচ্ছে নদীসমূহ। তাদের যখনই ফল-ফলাদি খেতে দেওয়া হবে তখনই তারা বলবে, 'এগুলোতো তারই মতো, যা আমাদেরকে পূর্বে জীবিকা হিসেবে দেওয়া হতো'। আর তাদের জন্য সেখানে রয়েছে পুতপবিত্র স্ত্রীগণ। তারা সেখানে চিরস্থায়ী থাকবে' (আল-বাক্বারা, ২৫)।&lt;/meaning&gt;
 &lt;p&gt;আল্লাহ তাঁর পবিত্র কালামে তাঁর মু'মিন বান্দাদের জন্য অফুরন্ত পুরস্কারের কথা ঘোষণা দিয়েছেন। আল্লাহ তাআলা বলেন,&lt;/p&gt;
@@ -564,8 +587,7 @@
 &lt;p&gt;পূর্ণ মু'মিন হওয়ার জন্য রাসূলুল্লাহ (ﷺ) বিভিন্ন সময় বিভিন্নভাবে বিভিন্ন গুণাবলীর কথা উল্লেখ করেছেন।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَة قَالَ : قَالَ رَسُولُ اللهِ ﷺ : «لَا تَدْخُلُونَ الْجَنَّةَ حَتَّى تُؤْمِنُوا، وَلَا تُؤْمِنُوا حَتَّى تَحَابُّوا، أَوَلَا أَدُلُّكُمْ عَلَى شَيْءٍ إِذَا فَعَلْتُمُوهُ تَحَابَبْتُمْ؟ أَفْشُوا السَّلَامَ بَيْنَكُمْ».&lt;/ar&gt;
 &lt;p&gt;আবু হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'তোমরা জান্নাতে প্রবেশ করতে পারবে না, যতক্ষণ না তোমরা ঈমান গ্রহণ করবে। আর তোমরা ঈমানদার বলে গণ্য হবে না, যতক্ষণ না তোমরা পরস্পরকে ভালোবাসবে। আমি কি তোমাদেরকে এমন কথা বলে দিব না, যা করলে তোমাদের পারস্পরিক ভালোবাসা বৃদ্ধি পাবে? তোমরা পরস্পরের মধ্যে সালামের প্রচলন করো' (ছহীহ মুসলিম, হা/২০৩; মুসনাদে আহমাদ, হা/৯০৭৩; মিশকাত, হা/৪৬৩১)।&lt;/p&gt;
-&lt;p&gt;প্রকৃত মু'মিন হওয়ার জন্য মুসলমান ভাই-বোন পরস্পরকে ভালবাসতে হবে একমাত্র আল্লাহ তাআলাকে সন্তুষ্ট করার জন্য। কিন্তু বর্তমান সমাজে পরস্পরকে ভালোবাসা নেই বললেই চলে। কেননা ভাই ভাইয়ের সাথে সম্পর্ক নেই, ভাই-বোনের সাথে সম্পর্ক নেই, সন্তানের পিতা-মাতার প্রতি&lt;/p&gt;
-&lt;p&gt;ভালোবাসা নেই। সমাজে চালু হয়েছে এক নোংরামী অবৈধ ভালোবাসা। যার কারণে নারী নির্যাতন থেকে শুরু করে সর্বধরনের অন্যায় অরাজকতা বেশি হয়েছে। মানুষের ঈমান না থাকার কারণেই মানুষ সর্বধরনের অন্যায় কাজে লিপ্ত হয়েছে।&lt;/p&gt;
+&lt;p&gt;প্রকৃত মু'মিন হওয়ার জন্য মুসলমান ভাই-বোন পরস্পরকে ভালবাসতে হবে একমাত্র আল্লাহ তাআলাকে সন্তুষ্ট করার জন্য। কিন্তু বর্তমান সমাজে পরস্পরকে ভালোবাসা নেই বললেই চলে। কেননা ভাই ভাইয়ের সাথে সম্পর্ক নেই, ভাই-বোনের সাথে সম্পর্ক নেই, সন্তানের পিতা-মাতার প্রতি ভালোবাসা নেই। সমাজে চালু হয়েছে এক নোংরামী অবৈধ ভালোবাসা। যার কারণে নারী নির্যাতন থেকে শুরু করে সর্বধরনের অন্যায় অরাজকতা বেশি হয়েছে। মানুষের ঈমান না থাকার কারণেই মানুষ সর্বধরনের অন্যায় কাজে লিপ্ত হয়েছে।&lt;/p&gt;
 &lt;p&gt;রাসূলুল্লাহ (ﷺ)-এর বাণী,&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ قَالَ : قَالَ رَسُولُ اللهِ : «الْحَيَاءُ مِنَ الْإِيمَانِ، وَالْإِيمَانُ فِي الْجَنَّةِ. وَالْبَذَاءُ مِنَ الْجَفَاءِ، وَالْجَفَاءُ فِي النَّارِ».&lt;/ar&gt;
 &lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'লজ্জা ঈমানের অঙ্গ। আর ঈমানের স্থান জান্নাতে। পক্ষান্তরে নির্লজ্জতা দুশ্চরিত্রের অঙ্গ। আর দুশ্চরিত্রের স্থান জাহান্নাম' (ইবনু মাজাহ, হা/৪১৮৪; তিরমিযী, হা/২০০৯; মুসনাদে আহমাদ, হা/১০৫১৯; মিশকাত, হা/৫০৭৭)।&lt;/p&gt;
@@ -587,12 +609,12 @@
 &lt;p&gt;আব্বাস ইবনু আব্দুল মুত্ত্বালিব (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে লোক আল্লাহকে প্রতিপালক, ইসলামকে দ্বীন এবং মুহাম্মাদ (ﷺ)-কে রাসূল হিসেবে পেয়ে সন্তুষ্ট, সে-ই ঈমানের প্রকৃত স্বাদ পেয়েছে' (ছহীহ মুসলিম, হা/১৬০; তিরমিযী, হা/২৬২৩; মিশকাত, হা/৯)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ اللهِ قَالَ : قَالَ رَسُولُ اللهِ اللهِ : وَاللهِ لَا يُؤْمِنُ، وَاللَّهِ لَا يُؤْمِنُ، وَاللَّهِ لَا يُؤْمِنُ ". قِيلَ : مَنْ يَا رَسُولَ اللهِ قَالَ : الَّذِي لَا يَأْمَنُ جَارُهُ بَوَائِقَهُ».&lt;/ar&gt;
 &lt;p&gt;আবু হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন,&lt;/p&gt;
-&lt;meaning&gt;অর্থ: 'আল্লাহর কসম! সে মু'মিন নয়। 'আল্লাহর কসম! সে মু'মিন নয়। 'আল্লাহর কসম! সে মু'মিন নয়। জিজ্ঞাসা করা হলো, হে আল্লাহর রাসূল! সেই ব্যক্তি কে? তিনি বললেন, যার অন্যায় থেকে তার প্রতিবেশী নিরাপদ থাকে না' (ছহীহ বুখারী, হা/৫০১৬; সিলসিলা ছহীহা, হা/৫৪৯; মিশকাত, হা/৪৯৬২)।&lt;/meaning&gt;
+&lt;meaning&gt;অর্থ: 'আল্লাহর কসম! সে মু'মিন নয়। 'আল্লাহর কসম! সে মু'মিন নয়। 'আল্লাহর কসম! সে মু'মিন নয়। জিজ্ঞাসা করা হলো, হে 'আল্লাহর রাসূল! সেই ব্যক্তি কে? তিনি বললেন, যার অন্যায় থেকে তার প্রতিবেশী নিরাপদ থাকে না' (ছহীহ বুখারী, হা/৫০১৬; সিলসিলা ছহীহা, হা/৫৪৯; মিশকাত, হা/৪৯৬২)।&lt;/meaning&gt;
 &lt;ar&gt;عَنِ ابْنِ عَبَّاسٍ قَالَ : سَمِعْتُ رَسُولُ اللهِ ﷺ يَقُولُ: «لَيْسَ الْمُؤْمِنُ بِالَّذِي يَشْبَعُ وَجَارُهُ جَائِعُ إِلَى جَنْبِهِ».&lt;/ar&gt;
 &lt;p&gt;আব্দুল্লাহ ইবনু আব্বাস (রাঃ) থেকে বর্ণিত, তিনি বলেন, 'আমি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছি, ঐ ব্যক্তি মু'মিন নয়, যে উদর পূর্ণ করে (পেট পূর্ণ করে) খায়, আর তার পাশেই তার প্রতিবেশী অভুক্ত থাকে' (বায়হাক্বী, হা/৫৬৬০; আদাবুল মুফরাদ, হা/১১২; সিলসিলা ছহীহা, হা/১৪৯; মিশকাত, হা/৪৯৯১)।&lt;/p&gt;
 &lt;p&gt;উপরিউক্ত আলোচনায় এক জন পূর্ণ মুমিনের বৈশিষ্ট্যাবলি ধারাবাহিকভাবে উল্লেখ করা হলো।&lt;/p&gt;
-&lt;p&gt;১. আল্লাহ তাআলাই একমাত্র ক্ষমতার অধিকারী এই বিশ্বাস রাখা। তার ক্ষমতার সাথে কাউকে সমকক্ষ মনে না করা এবং অন্যকে উপাস্য হিসেবে গ্রহণ না করা।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;২. আর মুহাম্মাদ (ﷺ)-কে শেষ নবী ও রাসূল হিসেবে মেনে নেওয়া। আল্লাহ তাআলা ও তাঁর রাসূলের প্রতি বিশ্বাসের সাথে আরও কয়েকটি বিষয়ের প্রতি বিশ্বাস রাখা। (ক) ফেরেশতাগণের প্রতি। অর্থাৎ ফেরেশতাগণ যে 'আল্লাহ তাআলার কর্মচারী, মানুষের জীবন বৃত্তান্তের লেখক' সেটা মনে প্রাণে বিশ্বাস করা।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;(খ) আখেরাতের প্রতি বিশ্বাস অর্থাৎ মৃত্যুই যে জীবনের শেষ নয়, বরং মৃত্যুর পর মানুষকে এক দিন পুনরুজ্জীবিত করা হবে এবং তার কর্মের বিচার করা হবে, সে বিষয়ে পূর্ণ বিশ্বাস রাখা। (গ) তাক্বদীরের ভাল-মন্দের উপর বিশ্বাস রাখা (অর্থাৎ আপ্রাণ চেষ্টার পর যেটা হয় সেটা তাক্বদীর হিসাবে বিশ্বাস করা, হা-হুতাশ না করা)।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;(ঘ) অদৃশ্য বিষয়সমূহের উপর বিশ্বাস রাখা যেমন: কবর, কিয়ামত, জান্নাত, জাহান্নাম। ৩. অবনত হয়ে ভয়ভীতি নিয়ে ছালাত আদায় করা। ৪. পিতা-মাতা ভাই-বোন, ছেলে-মেয়ে সবার চেয়ে রাসূলুল্লাহ (ﷺ)-কে বেশি ভালোবাসা। অর্থাৎ তাঁর সুন্নাত পালনে কারো তোয়াক্কা না করা।&lt;/p&gt;
-&lt;p&gt;৫. আমানত রক্ষা করা, ওয়াদা রক্ষা করা। কারণ; এ দুটি স্বভাব রক্ষা না করা মুনাফিকের লক্ষণ।&lt;/p&gt;
+&lt;p&gt;১. আল্লাহ তাআলাই একমাত্র ক্ষমতার অধিকারী এই বিশ্বাস রাখা। তার ক্ষমতার সাথে কাউকে সমকক্ষ মনে না করা এবং অন্যকে উপাস্য হিসেবে গ্রহণ না করা।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;২. আর মুহাম্মাদ (ﷺ)-কে শেষ নবী ও রাসূল হিসেবে মেনে নেওয়া। আল্লাহ তাআলা ও তাঁর রাসূলের প্রতি বিশ্বাসের সাথে আরও কয়েকটি বিষয়ের প্রতি বিশ্বাস রাখা।&lt;br&gt;(ক) ফেরেশতাগণের প্রতি। অর্থাৎ ফেরেশতাগণ যে 'আল্লাহ তাআলার কর্মচারী, মানুষের জীবন বৃত্তান্তের লেখক সেটা মনে প্রাণে বিশ্বাস করা।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;(খ) আখেরাতের প্রতি বিশ্বাস অর্থাৎ মৃত্যুই যে জীবনের শেষ নয়, বরং মৃত্যুর পর মানুষকে এক দিন পুনরুজ্জীবিত করা হবে এবং তার কর্মের বিচার করা হবে, সে বিষয়ে পূর্ণ বিশ্বাস রাখা।&lt;br&gt;(গ) তাক্বদীরের ভাল-মন্দের উপর বিশ্বাস রাখা (অর্থাৎ আপ্রাণ চেষ্টার পর যেটা হয় সেটা তাক্বদীর হিসাবে বিশ্বাস করা, হা-হুতাশ না করা)।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;(ঘ) অদৃশ্য বিষয়সমূহের উপর বিশ্বাস রাখা যেমন: কবর, কেয়ামত, জান্নাত, জাহান্নাম।&lt;br&gt;৩. অবনত হয়ে ভয়ভীতি নিয়ে ছালাত আদায় করা।&lt;br&gt;৪. পিতা-মাতা ভাই-বোন, ছেলে-মেয়ে সবার চেয়ে রাসূলুল্লাহ (ﷺ)-কে বেশি ভালোবাসা। অর্থাৎ তাঁর সুন্নাত পালনে কারো তোয়াক্কা না করা।&lt;/p&gt;
+&lt;p&gt;৫. আমানত রক্ষা করা, ওয়াদা রক্ষা করা। কারণ; এ দুটি স্বভাব রক্ষা না করা মুনাফিক্কের লক্ষণ।&lt;/p&gt;
 &lt;p&gt;৬. পরস্পরকে আল্লাহ তাআলার সন্তুষ্টির উদ্দেশ্যে ভালোবাসা। তাই নিজের জন্য যেটা পছন্দ, সেটা অন্যের জন্যও পছন্দ করা।&lt;/p&gt;
 &lt;p&gt;৭. লজ্জা করা, কারণ যার লজ্জা নেই, তার ঈমান নেই।&lt;/p&gt;
 &lt;p&gt;৮. প্রতিবেশীর কোন ক্ষতি না করা। কষ্ট না দেওয়া। কারণ প্রতিবেশীর হক্ক অতীব কঠিন।&lt;/p&gt;
@@ -600,34 +622,7 @@
 &lt;p&gt;অতঃপর মানবীয় সবগুণাবলি থাকাই হচ্ছে পূর্ণ মুমিনের কাজ।&lt;/p&gt;
 &lt;p&gt;১০. আর প্রকৃত মুমিনের জন্য সবচেয়ে গুরুত্বপূর্ণ কাজ হচ্ছে, সর্ব অবস্থায় আল্লাহ তাআলার উপর ভরসা করা।&lt;/p&gt;
 &lt;ar&gt;إِنَّهَا الْمُؤْمِنُونَ الَّذِينَ إِذَا ذُكِرَ اللَّهُ وَجِلَتْ قُلُوبُهُمْ وَإِذَا تُلِيَتْ عَلَيْهِمْ آيَاتُهُ زَادَتْهُمْ إِيمَانًا وَعَلَى رَبِّهِمْ يَتَوَكَّلُونَ الَّذِينَ يُقِيمُونَ الصَّلَاةَ وَمِمَّا رَزَقْنَاهُمْ يُنْفِقُونَ أُولَئِكَ هُمُ الْمُؤْمِنُونَ حَقًّا لَهُمْ دَرَجَاتٌ عِنْدَ رَبِّهِمْ وَمَغْفِرَةٌ وَرِزْقٌ كَرِيمٌ.&lt;/ar&gt;
-&lt;p&gt;'মু'মিন তো তারাই, যাঁদের সামনে আল্লাহ তাআলার কথা স্মরণ করা হলে, তাদের অন্তর কেঁপে ওঠে। আর যখন তাঁদের সামনে আল্লাহ তাআলার আয়াত পাঠ করা হয়, তখন তা তাঁদের ঈমানকে বৃদ্ধি করে। তাঁরা ছালাত কায়েম করে এবং আমার দেওয়া রিযিক হতে দান করে। এরাই হলো প্রকৃত মু'মিন, যাঁদের জন্য তাঁদের প্রতিপালকের নিকটে রয়েছে অগণিত মর্যাদা, ক্ষমা ও সম্মানজনক রিযিকের ব্যবস্থা' (আল-আনফাল, ১-৪)।&lt;/p&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>নারী ও পুরুষের আদর্শ</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>তৃতীয় আদর্শ</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>&lt;div class="page-text"&gt;&lt;p&gt;আল্লাহর দিকে মনোনিবেশকারী পুরুষ ও স্ত্রীলোক। এমন পুরুষ ও স্ত্রীলোকের কথা আল্লাহ এখানে বলেছেন, যাদের অন্তর ও দেহের সকল অঙ্গ-প্রত্যঙ্গ সর্বদা আল্লাহর বিধান পালনে মশগুল।&lt;/p&gt;
-&lt;p&gt;আল্লাহ তাআলা বলেন,&lt;/p&gt;
-&lt;ar&gt;أَمَّنْ هُوَ قَانِتٌ آنَاءَ اللَّيْلِ سَاجِداً وَقَابِما يَحْذَرُ الْآخِرَةَ وَيَرْجُو رَحْمَةَ রَبِّهِ.&lt;/ar&gt;
-&lt;p&gt;'যে ব্যক্তি রাত্রিকালে সিজদার মাধ্যমে অথবা দাঁড়িয়ে ইবাদত করে, পরকালের ভয় রাখে ও তার পালনকর্তার রহমতের প্রত্যাশা করে' (আয- ঘুমার, ৯)।&lt;/p&gt;&lt;/div&gt;</t>
+&lt;p&gt;'মু'মিন তো তারাই, যাঁদের সামনে আল্লাহ তাআলার কথা স্মরণ করা হলে, তাদের অন্তর কেঁপে ওঠে। আর যখন তাঁদের সামনে আল্লাহ তাআলার আয়াত পাঠ করা হয়, তখন তা তাঁদের ঈমানকে বৃদ্ধি করে। তাঁরা ছালাত কায়েম করে এবং আমার দেওয়া রিযিক্ক হতে দান করে। এরাই হলো প্রকৃত মু'মিন, যাঁদের জন্য তাঁদের প্রতিপালকের নিকটে রয়েছে অগণিত মর্যাদা, ক্ষমা ও সম্মানজনক রিযিকের ব্যবস্থা' (আল-আনফাল, ১-৪)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr"/>
@@ -646,10 +641,62 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>তৃতীয় আদর্শ</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>&lt;div class="page-text"&gt;&lt;p&gt;আল্লাহর দিকে মনোনিবেশকারী পুরুষ ও স্ত্রীলোক। এমন পুরুষ ও স্ত্রীলোকের কথা আল্লাহ এখানে বলেছেন, যাদের অন্তর ও দেহের সকল অঙ্গ-প্রত্যঙ্গ সর্বদা আল্লাহর বিধান পালনে মশগুল।&lt;/p&gt;
+&lt;p&gt;আল্লাহ তাআলা বলেন,&lt;/p&gt;
+&lt;ar&gt;أَمَّنْ هُوَ قَانِتٌ آنَاءَ اللَّيْلِ سَاجِداً وَقَابِما يَحْذَرُ الْآخِرَةَ وَيَرْجُو رَحْمَةَ রَبِّهِ.&lt;/ar&gt;
+&lt;p&gt;'যে ব্যক্তি রাত্রিকালে সিজদার মাধ্যমে অথবা দাঁড়িয়ে ইবাদত করে, পরকালের ভয় রাখে ও তার পালনকর্তার রহমতের প্রত্যাশা করে' (আয- ঘুমার, ৯)।&lt;/p&gt;
+&lt;p&gt;আল্লাহ তাআলা এখানে নারী-পুরুষের একটি বড় গুণ উল্লেখ করেছেন। আর তা হচ্ছে রাত জেগে ইবাদত করা, যা নবী-রাসূল ও বড় ইবাদতগুজার লোকদের আদর্শ। আল্লাহ অন্যত্র বলেন,&lt;/p&gt;
+&lt;ar&gt;وَلَهُ مَنْ فِي السَّمَاوَاتِ وَالْأَرْضِ كُلٌّ لَهُ قَانِتُونَ.&lt;/ar&gt;
+&lt;p&gt;'আকাশ ও যমীনে যা কিছু আছে সবাই তাঁর একনিষ্ঠভাবে ইবাদত করে' (আর-রূম, ২৬)। আল্লাহ তাআলা অন্যত্র আয়াতে বলেন,&lt;/p&gt;
+&lt;ar&gt;وَمِنَ اللَّيْلِ فَاسْجُدُ لَهُ وَسَبِّحْهُ لَيْلًا طَوِيلًا.&lt;/ar&gt;
+&lt;p&gt;'আর রাতের কিছু অংশ তাঁর জন্য সিজদায় অবনত হও। আর রাতের দীর্ঘ সময় ধরে তাঁর তাসবীহ পাঠ করো' (আদ-দাহার, ২৬)। আল্লাহ তাআলা অন্যত্র বলেন,&lt;/p&gt;
+&lt;ar&gt;وَقُومُوا لِلَّهِ قَانِتِينَ.&lt;/ar&gt;
+&lt;p&gt;'আর আল্লাহর সামনে একান্ত আদবের সাথে ইবাদতের জন্য দাঁড়িয়ে যাও' (আল-বাক্বারা, ২৩৮)। আল্লাহ সুবহানাহু তাআলা অন্য এক আয়াতে বলেন,&lt;/p&gt;
+&lt;ar&gt;وَاذْكُرِ اسْمَ রَبِّكَ وَتَبَتَّلُ إِلَيْهِ تَبْتِيلًا.&lt;/ar&gt;
+&lt;p&gt;'তুমি তোমার প্রতিপ্রতিপালকের নাম স্মরণ করো এবং একাগ্রচিত্তে তাঁর প্রতি মগ্ন হও (আল-মুযযামমিল, ৮)।&lt;/p&gt;
+&lt;p&gt;আদর্শ নারী-পুরুষের জন্য রাতের ইবাদত একটি গুরুত্বপূর্ণ বিষয়।&lt;/p&gt;
+&lt;ar&gt;قَالَتْ عَائِشَةُ : حَتَّى تَفَطَّرَ قَدَمَاهُ . وَالْفُطُورُ الشُّقُوقُ ، ( انْفَطَرَتْ انْشَقَّتْ .&lt;/ar&gt;
+&lt;p&gt;আয়েশা (রাঃ) বলেছেন, এমনকি তাঁর রাসূল (ﷺ)-এর দুটি পা ফেটে যেতো। والفطور অর্থ 'ফেটে যাওয়া' إنفطرت, ফেটে গেল (ছহীহ বুখারী, হা/১১৩০; অধ্যায়-৬ 'নবী (ﷺ)-এর তাহজ্জুদের ছালাতে দীর্ঘক্ষণ দাঁড়ানোর ফলে তাঁর উভয় পা ফুলে যেতো')।&lt;/p&gt;
+&lt;ar&gt;عَنْ زِيَادٍ قَالَ : سَمِعْتُ الْمُغِيرَةَ الله يَقُولُ : إِنْ كَانَ النَّبِيُّ ﷺ لَيَقُومُ لِيُصَلَّى حَتَّى تَرِمَ قَدَمَاهُ أَوْ سَاقَاهُ ، فَيُقَالُ لَهُ فَيَقُولُ : ( أَفَلَا أَكُونُ عَبْدًا شَكُورًا ».&lt;/ar&gt;
+&lt;p&gt;মুগীরা (রাঃ) হতে বর্ণিত। তিনি বলেন, নবী (ﷺ) ছালাত আদায় করতেন; এমনকি তার পদযুগল অথবা তার দুপায়ের গোছা ফুলে যেত। তখন এ ব্যাপারে তাঁকে বলা হলে তিনি বলতেন, 'আমি কি একজন শুকরিয়া আদায়কারী বান্দাহ হব না'? (ছহীহ বুখারী, হা/১১৩০)।&lt;/p&gt;
+&lt;p&gt;তৃতীয় আদর্শে এমন পুরুষ ও স্ত্রীলোকের কথা বলা হয়েছে, যাদের অন্তর ও দেহের সকল অঙ্গ-প্রত্যঙ্গ সর্বদা আল্লাহর বিধান পালনে মশগুল। অর্থাৎ, খালেস নিয়‍্যাতে (একনিষ্ঠভাবে) আল্লাহর বিধান পালন করে। যেমন আল্লাহ তাআলা বলেন,&lt;/p&gt;
+&lt;ar&gt;فَاسْتَجَابَ لَهُمْ رَبُّهُمْ أَنِّي لَا أُضِيعُ عَمَلَ عَامِلٍ مِنْكُمْ مِنْ ذَكَرٍ أَوْ أُنْثَى بَعْضُكُمْ مِنْ بَعْضٍ فَالَّذِينَ هَاجَرُوا وَأُخْرِجُوا مِنْ دِيَارِهِمْ وَأُوذُوا فِي سَبِيلِي وَقَاتَلُوا وَقُتِلُوا لَا كَفِّرَنَّ عَنْهُمْ سَيِّئَاتِهِمْ وَلَا دْখِلَنَّهُمْ جَنَّاتٍ تَجْرِي مِنْ تَحْتِهَا الْأَنْهَارُ ثَوَابًا مِنْ عِنْدِ اللَّهِ وَاللَّهُ عِنْدَهُ حُسْنُ الثَّوَابِ.&lt;/ar&gt;
+&lt;p&gt;'তখন তাদের প্রতিপালক তাদের ডাকে সাড়া দিয়ে বললেন, অবশ্যই আমি তোমাদের মধ্য থেকে কোন নর-নারীর আমলকে বিনষ্ট করি না। কারণ; তোমরা একে অন্যের অংশ। আর যারা হিযরত করেছে, যাদেরকে তাদের ঘর-বাড়ি হতে বের করে দেওয়া হয়েছে, আমার রাস্তায় যাদেরকে কষ্ট দেওয়া হয়েছে (অর্থাৎ, অত্যাচারিত ও নির্যাতিত হয়েছে) এবং যারা লড়াই করেছে এবং নিহত (শহীদ) হয়েছে, অবশ্যই অবশ্যই আমি তাদের গুনাহসমূহ ক্ষমা করে দিব এবং অবশ্যই অবশ্যই আমি তাদের এমন জান্নাতে প্রবেশ করাব, যার তলদেশ দিয়ে ঝর্ণাধারা প্রবহমান।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;আর এই জান্নাতই তাদের জন্য আল্লাহ তাআলার পক্ষ থেকে মহাপ্রতিদান। প্রকৃতপক্ষে, আল্লাহর নিকটেই রয়েছে উত্তম প্রতিদান (আল-ইমরান, ১৯৫)।&lt;/p&gt;
+&lt;p&gt;আল্লাহ তাআলা বলেন,&lt;/p&gt;
+&lt;ar&gt;وَمَا أُمِرُوا إِلَّا لِيَعْبُدُوا اللَّهَ مُخْلِصِينَ ...&lt;/ar&gt;
+&lt;p&gt;'আর তাদেরকে শুধু এই নির্দেশই দেওয়া হয়েছে যে, তারা একনিষ্ঠভাবে (অর্থাৎ, ইখলাস সহকারে) আল্লাহ তাআলার ইবাদত করবে'... (আল-বায়্যিনাহ, ৫)।&lt;/p&gt;
+&lt;ar&gt;عَنْ عَبْدِ اللَّهِ بْنِ مَسْعُودٍ الله يُحَدِّثُ عَنْ أَبِيهِ عَنِ النَّبِيَّ ﷺ قَالَ : « نَضَّرَ اللَّهُ امْرَأَ سَمِعَ مَقَالَتِي فَوَعَاهَا وَحَفِظَهَا وَبَلَّغَهَا فَرُبَّ حَامِلِ فِقْهِ إِلَى মَنْ هُوَ أَفْقَهُ مِنْهُ ثَلَاتٌ لَا يُغلُّ عَلَيْهِنَّ قَلْبُ مُسْلِمٍ إِخْلَاصُ الْعَمَلِ لِلَّهِ وَمُنَاصَحَةُ أَئِمَّةِ الْمُسْلِمِينَ وَلُزُومِ جَمَاعَتِهِمْ فَإِنَّ الدَّعْوَةَ تُحِيطُ مِنْ وَرَائِهِمْ ».&lt;/ar&gt;
+&lt;p&gt;আব্দুল্লাহ ইবনু মাসউদ (রাঃ) তাঁর পিতা হতে বর্ণনা করেন, তাঁর পিতা নবী (ﷺ) হতে বর্ণনা করেন, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'আল্লাহ সে ব্যক্তির মুখ উজ্জ্বল করুন, যে আমার কোন কথা শুনেছে, অতঃপর এ কথাকে স্মরণ রেখেছে ও রক্ষা করেছে এবং যা শুনেছে হুবহু তা মানুষের নিকট পৌঁছিয়ে দিয়েছে। কারণ জ্ঞানের অনেক বাহক নিজে জ্ঞানী নয়। আবার কেউ কেউ এমন আছে যারা নিজেরা জ্ঞানী হলেও, নিজের তুলনায় বড় জ্ঞানীর নিকট জ্ঞান বহন করে নিয়ে যায়।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;তিনটি বিষয়ে মুসলিমের অন্তর বিশ্বাসঘাতকতা (অবহেলা) করতে পারে না- ১. আল্লাহর উদ্দেশ্যে (ইখলাসসহ) অর্থাৎ নিষ্ঠার সাথে কাজ করা, ২. মুসলিমদের কল্যাণ কামনা করা এবং ৩. মুসলিমের জামা'আতকে আঁকড়ে ধরা। কারণ মুসলিমদের দোয়া বা আহ্বান তাদের পরবর্তী (মুসলিমদেরও) শামিল করে রাখে' (তিরমিযী, হা/২৬৫৮; মুসনাদে আহমাদ, হা/১৬৭৮৪; মিশকাত, হা/২২৮)।&lt;/p&gt;
+&lt;ar&gt;عَنْ مُعَاذِ بْنِ جَبَلِ الله قَالَ: قَالَ النَّبِيُّ ﷺ : « يَا مُعَاذُ أَتَدْرِي مَا حَقُّ اللَّهِ عَلَى الْعِبَادِ » . قَالَ : اللهُ وَرَسُولُهُ أَعْلَمُ . قَالَ : ( أَنْ يَعْبُدُوهُ وَلَا يُشْرِكُوا بِهِ شَيْئًا ، أَتَدْرِي مَا حَقُّهُمْ عَلَيْهِ». قَالَ : اللهُ وَرَسُولُهُ أَعْلَمُ . قَالَ : " أَنْ لَا يُعَذِّبَهُمْ ».&lt;/ar&gt;
+&lt;p&gt;মু'আজ (রাঃ) হতে বর্ণিত, রাসূলুল্লাহ (ﷺ) তাকে বলেছেন, 'হে মু'আজ! তুমি কি জান বান্দার প্রতি আল্লাহর হক্ক কী? 'তখন আমি বললাম, 'আল্লাহ ও তাঁর রাসূলই ভালো জানেন'। তিনি বললেন,' বান্দার প্রতি আল্লাহর হক্ক হচ্ছে, তারা (বান্দাগণ) শুধু তাঁরই ইবাদত করবে এবং তাঁর সাথে অন্য কাউকে শরীক করবে না। অর্থাৎ, ইখলাস সহকারে তাঁর ইবাদত করবে।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;তিনি বললেন, 'হে মু'আজ! তুমি কি জান আল্লাহর প্রতি বান্দার হক্ক কী? 'তখন আমি বললাম, 'আল্লাহ ও তাঁর রাসূলই ভাল জানেন'। তিনি বললেন, 'আল্লাহর প্রতি বান্দাহর হক্ক হচ্ছে, (বান্দাগণ ইখলাস সহকারে তাঁর ইবাদত করলে) তিনি তাদেরকে শাস্তি দিবেন না' (ছহীহ বুখারী, হা/৭৩৭৩; ছহীহ মুসলিম, হা/১৫৪)।&lt;/p&gt;
+&lt;p&gt;উপরিউক্ত আলোচনা হতে এটাই প্রতীয়মান হয় যে, আদর্শ নারী-পুরুষ হিসাবে একমাত্র একনিষ্ঠ ভাবে আল্লাহর ইবাদত করা (শুকুর-গুজার, তাসবীহ-তাহলীল পাঠ করা)।&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>নারী ও পুরুষের আদর্শ</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>চতুর্থ আদর্শ</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;সত্য ও ন্যায়-নিষ্ঠ পুরুষ ও স্ত্রীলোক। সততা নারী-পুরুষের জন্য একটি প্রশংসনীয় আদর্শ। সততা এমন ঈমানের পরিচায়ক যার পরিণাম জান্নাত। সত্য যে একটি মহৎ গুণ এবং তার পরিণাম যে জান্নাত, সে ব্যাপারে মহান আল্লাহ বলেন,&lt;/p&gt;
 &lt;ar&gt;وَالْعَصْرِ إِنَّ الْإِنْسَانَ لَفِي خُسْرٍ إِلَّا الَّذِينَ آمَنُوا وَعَمِلُوا الصَّالِحَاتِ وَتَوَاصَوْا بِالْحَقِّ وَتَوَاصَوْا بِالصَّبْرِ.&lt;/ar&gt;
@@ -664,43 +711,42 @@
 &lt;ar&gt;عَنِ الْحَسَنِ بْنِ عَلِيَّ قَالَ : حَفِظْتُ مِنْ رَسُولِ اللهِ ﷺ دَعْ مَا يَرِيبُكَ إِلَى مَا لَا يُرِيبُكَ، فَإِنَّ الصَّدْقَ طُمَأْنِينَةُ، وَإِنَّ الْكَذِبَ رِيبَةٌ».&lt;/ar&gt;
 &lt;p&gt;হাসান ইবনু আলী (রাঃ) হতে বর্ণিত। তিনি বলেন, আমি রাসূলুল্লাহ (ﷺ)-এর বাণীটি মুখস্থ করে রেখেছি যে, 'যে কাজ মনের মধ্যে সন্দেহ সৃষ্টি করে, সে কাজ পরিহার করে সন্দেহমুক্ত কাজ করো। কারণ; সত্য ও ন্যায়ের মধ্যে প্রশান্তি আছে, আর মিথ্যা ও অন্যায়ের মধ্যে দ্বিধা-দ্বন্দের সৃষ্টি হয়' (তিরমিযী, হা/২৫১৮; নাসাঈ, হা/৫৩৯৮; মিশকাত, হা/২৭৭৩)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ اللهُ عَنِ النَّبِيَّ ﷺ قَالَ : « آيَةُ الْمُنَافِقِ ثَلَاثُ إِذَا حَدَّثَ كَذَبَ ، وَإِذَا وَعَدَ أَخْلَفَ ، وَإِذَا اؤْتُمِنَ خَانَ » . وَزَادَ مُسْلِمُ : وَإِنْ صَامَ وَصَلَّى وَزَعَمَ أَنَّهُ مُسْلِمٌ.&lt;/ar&gt;
-&lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'মুনাফিকের নিদর্শন তিনটি- ১. যখন কথা বলে মিথ্যা বলে; ২. ওয়াদা করলে ভঙ্গ করে; ৩. তার নিকটে কোন আমানত রাখলে তার খেয়ানত (বিশ্বাসঘাতকতা) করে। ইমাম মুসলিম (রহঃ)-এর বর্ণনায় আরো আছে, 'যদিও সে ছিয়াম পালন করে, ছালাত আদায় করে, আর ধারণা করে সে (পূর্ণ) মুসলিম' (ছহীহ বুখারী, হা/৩৩; ছহীহ মুসলিম, হা/১০৯, ২২২; মিশকাত, হা/৫৫)।&lt;/p&gt;
-&lt;ar&gt;أَنَّ عَبْدَ اللَّهِ بْنَ كَعْبِ بْنِ مَالِكَ  ... فَجِئْتُهُ فَلَمَّا سَلَّمْتُ عَلَيْهِ تَبَسَّمَ تَبَسُّمَ الْمُغْضَبِ ، ثُمَّ قَالَ « تَعَالَ » . فَجِئْتُ أَمْشِي حَتَّى جَلَسْتُ بَيْنَ يَدَيْهِ ، فَقَالَ لِي « مَا خَلَّفَكَ أَلَمْ تَكُنْ قَدِ ابْتَعْتَ ظَهْرَكَ » . فَقُلْتُ : بَلَى ، إِنِّى وَاللهِ لَوْ جَلَسْتُ عِنْدَ غَيْرِكَ مِنْ أَهْلِ الدُّنْيَا ، لَرَأَيْتُ أَنْ سَأَخْرُجُ مِنْ سَخَطِهِ بِعُذْرٍ ، وَلَقَدْ أُعْطِيتُ جَدَلاً ، وَلَكِنَّى وَاللَّهِ لَقَدْ عَلِمْتُ لَئِنْ حَدَّثْتُكَ الْيَوْمَ حَدِيثَ كَذِبٍ تَرْضَى بِهِ عَنِّى لَيُوشِكَنَّ اللَّهُ أَنْ يُسْخِطَكَ عَلَى ، وَلَئِنْ حَدَّثْتُكَ حَدِيثَ صِدْقٍ تَদُ عَلَى فِيهِ إِنِّي لأَرْجُو فِيهِ عَفْوَ اللَّهِ ، لَا وَاللَّهِ مَا كَانَ لِي مِنْ عُذْرٍ ، وَاللَّهِ مَا كُنْتُ قَطُّ أَقْوَى وَلاَ أَيْسَرَ مِنِّي حِينَ تَخَلَّفْتُ عَنْكَ . فَقَالَ رَسُولُ اللهِ ﷺ : « أَمَّا هَذَا فَقَدْ صَدَقَ ، فَقُمْ حَتَّى يَقْضِيَ اللَّهُ فِيكَ » . فَقُمْتُ حَتَّى كَمَلَتْ لَنَا خَمْسُونَ لَيْلَةً مِنْ حِينِ نَهَى رَسُولُ اللهِ ﷺ عَنْ كَلامِنَا ، فَلَمَّا صَلَّيْتُ صَلَاةَ الْفَجْرِ صُبْحَ خَمْسِينَ لَيْلَةً ، وَأَنَا عَلَى ظَهْرِ بَيْتٍ مِنْ بُيُوتِنَا ، فَبَيْنَا أَنَا جَالِسٌ عَلَى الْحَالِ الَّتِي ذَكَرَ اللهُ -&lt;/ar&gt;
-&lt;ar&gt;لَقَدْ تَابَ اللهُ عَلَى النَّبِيِّ وَالْمُهَاجِرِينَ وَالأَنْصَارِ الَّذِينَ اتَّبَعُوهُ فِي سَاعَةِ الْعُسْرَةِ مِنْ بَعْدِ مَا كَادَ يَزِيعُ قُلُوبُ فَرِيقٍ مِنْهُمْ ثُمَّ تَابَ عَلَيْهِمْ إِنَّهُ بِهِمْ رَءُوفٌ رَحِيمٌ وَعَلَى الثَّلَاثَةِ الَّذِينَ خُلِّفُوا حَتَّى إِذَا ضَاقَتْ عَلَيْهِمُ الْأَرْضُ بِمَا رَحُبَتْ وَضَاقَتْ عَلَيْهِمْ أَنْفُسُهُمْ وَظَنُّوا أَنْ لَا مَلْجَأَ مِنَ اللَّهِ إِلَّا إِلَيْهِ ثُمَّ تَابَ عَلَيْهِمْ لِيَتُوبُوا إِنَّ اللهَ هُوَ التَّوَّابُ الرَّحِيمُ - يَا أَيُّهَا الَّذِينَ آمَنُوا اتَّقُوا اللَّهَ وَكُونُوا مَعَ الصَّادِقِينَ قَدْ ضَاقَتْ عَلَى نَفْسِي ، وَضَاقَتْ عَلَى الأَرْضُ بِمَا رَحُبَتْ ، سَمِعْتُ صَوْتَ صَارِجٌ أَوْفَى عَلَى جَبَلِ سَلْعِ بِأَعْلَى صَوْتِهِ يَا كَعْبُ بْنَ مَالِكٍ ، أَبْشِرْ . قَالَ فَخَرَرْتُ سَاجِدًا ، وَعَرَفْتُ أَنْ قَدْ جَاءَ فَرَجُ ... إِنَّ اللَّهَ إِنَّمَا نَجَانِي بِالصِّدْقِ ، وَإِنَّ مِنْ تَوْبَتِي أَنْ لَا أُحَدِّثَ إِلَّا صِدْقًا مَا بَقِيتُ ، فَوَاللَّهِ مَا أَعْلَمُ أَحَدًا مِنَ الْمُسْلِمِينَ أَبْلاَهُ اللهُ فِي صِدْقِ الْحَدِيثِ مُنْذُ ذَكَرْتُ ذَلِكَ لِرَسُولِ اللهِ ﷺ أَحْسَنَ مِمَّا أَبْلَانِي ، مَا تَعَمَّدْتُ مُنْذُ ذَكَرْتُ ذَلِكَ لِرَسُولِ اللَّهِ اللَّهِ إِلَى يَوْমِي هَذَا كَذِبًا ، وَإِنِّي لَأَرْجُو أَنْ يَحْفَظَنِي اللَّهُ فِيمَا بَقِيتُ&lt;/ar&gt;
+&lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'মুনাফিকের নিদর্শন তিনটি- ১. যখন কথা বলে মিথ্যা বলে; ২. ওয়াদা করলে ভঙ্গ করে; ৩. তার নিকটে কোন আমানত রাখলে তার খেয়ানত (বিশ্বাসঘাতকতা) করে। ইমাম মুসলিম (রহঃ)-এর বর্ণনায় আরো আছে, 'যদি সে ছিয়াম পালন করে, ছালাত আদায় করে, আর ধারণা করে সে (পূর্ণ) মুসলিম' (ছহীহ বুখারী, হা/৩৩; ছহীহ মুসলিম, হা/১০৯, ২২২; মিশকাত, হা/৫৫)।&lt;/p&gt;
+&lt;ar&gt;أَنَّ عَبْدَ اللَّهِ بْنَ كَعْبِ بْنِ مَالِكَ  ... فَجِئْتُهُ فَلَمَّا سَلَّمْتُ عَلَيْهِ تَبَسَّمَ تَبَسُّمَ الْمُغْضَبِ ، ثُمَّ قَالَ « تَعَالَ » . فَجِئْتُ أَمْشِي حَتَّى جَلَسْتُ بَيْنَ يَدَيْهِ ، فَقَالَ لِي « مَا خَلَّفَكَ أَلَمْ تَكُنْ قَدِ ابْتَعْتَ ظَهْرَكَ » . فَقُلْتُ : بَلَى ، إِنِّى وَاللهِ لَوْ جَلَسْتُ عِنْدَ غَيْرِكَ مِنْ أَهْلِ الدُّنْيَا ، لَرَأَيْتُ أَنْ سَأَخْرُجُ مِنْ سَخَطِهِ بِعُذْرٍ ، وَلَقَدْ أُعْطِيتُ جَدَلاً ، وَلَكِنَّى وَاللَّهِ لَقَدْ عَلِمْتُ لَئِنْ حَدَّثْتُكَ الْيَوْمَ حَدِيثَ كَذِبٍ تَرْضَى بِهِ عَنِّى لَيُوشِكَنَّ اللَّهُ أَنْ يُسْخِطَكَ عَلَى ، وَلَئِنْ حَدَّثْتُكَ حَدِيثَ صِدْقٍ تَদُ عَلَى فِيهِ إِنِّي لأَرْجُو فِيهِ عَفْوَ اللَّهِ ، لَا وَاللَّهِ مَا كَانَ لِي مِنْ عُذْرٍ ، وَاللَّهِ مَا كُنْتُ قَطُّ أَقْوَى وَلاَ أَيْسَرَ مِنِّي حِينَ تَخَلَّفْتُ عَنْكَ . فَقَالَ رَسُولُ اللهِ ﷺ : « أَمَّا هَذَا فَقَدْ صَدَقَ ، فَقُمْ حَتَّى يَقْضِيَ اللَّهُ فِيكَ » . فَقُمْتُ حَتَّى كَمَلَتْ لَنَا خَمْسُونَ لَيْلَةً مِنْ حِينِ نَهَى رَسُولُ اللهِ ﷺ عَنْ كَلامِنَا ، فَلَمَّا صَلَّيْتُ صَلَاةَ الْفَجْرِ صُبْحَ خَمْسِينَ لَيْلَةً ، وَأَنَا عَلَى ظَهْرِ بَيْتٍ مِنْ بُيُوتِنَا ، فَبَيْنَا أَنَا جَالِسٌ عَلَى الْحَالِ الَّتِي ذَكَرَ اللهُ - لَقَدْ تَابَ اللهُ عَلَى النَّبِيِّ وَالْمُهَاجِرِينَ وَالأَنْصَارِ الَّذِينَ اتَّبَعُوهُ فِي سَاعَةِ الْعُسْرَةِ مِنْ بَعْدِ مَا كَادَ يَزِيعُ قُلُوبُ فَرِيقٍ مِنْهُمْ ثُمَّ تَابَ عَلَيْهِمْ إِنَّهُ بِهِمْ رَءُوفٌ رَحِيمٌ وَعَلَى الثَّلَاثَةِ الَّذِينَ خُلِّفُوا حَتَّى إِذَا ضَاقَتْ عَلَيْهِمُ الْأَرْضُ بِمَا رَحُبَتْ وَضَاقَتْ عَلَيْهِمْ أَنْفُسُهُمْ وَظَنُّوا أَنْ لَا مَلْجَأَ مِنَ اللَّهِ إِلَّا إِلَيْهِ ثُمَّ تَابَ عَلَيْهِمْ لِيَتُوبُوا إِنَّ اللهَ هُوَ التَّوَّابُ الرَّحِيمُ - يَا أَيُّهَا الَّذِينَ آمَنُوا اتَّقُوا اللَّهَ وَكُونُوا مَعَ الصَّادِقِينَ قَدْ ضَاقَتْ عَلَى نَفْسِي ، وَضَاقَتْ عَلَى الأَرْضُ بِمَا رَحُبَتْ ، سَمِعْتُ صَوْتَ صَارِجٌ أَوْفَى عَلَى جَبَلِ سَلْعِ بِأَعْلَى صَوْتِهِ يَا كَعْبُ بْنَ مَالِكٍ ، أَبْشِرْ . قَالَ فَخَرَرْتُ سَاجِدًا ، وَعَرَفْتُ أَنْ قَدْ جَاءَ فَرَجُ ... إِنَّ اللَّهَ إِنَّمَا نَجَانِي بِالصِّدْقِ ، وَإِنَّ مِنْ تَوْبَتِي أَنْ لَا أُحَدِّثَ إِلَّا صِدْقًا مَا بَقِيتُ ، فَوَاللَّهِ مَا أَعْلَمُ أَحَدًا مِنَ الْمُسْلِمِينَ أَبْلاَهُ اللهُ فِي صِدْقِ الْحَدِيثِ مُنْذُ ذَكَرْتُ ذَلِكَ لِرَسُولِ اللهِ ﷺ أَحْسَنَ مِمَّا أَبْلَانِي ، مَا تَعَمَّدْتُ مُنْذُ ذَكَرْتُ ذَلِكَ لِرَسُولِ اللَّهِ اللَّهِ إِلَى يَوْমِي هَذَا كَذِبًا ، وَإِنِّي لَأَرْجُو أَنْ يَحْفَظَنِي اللَّهُ فِيمَا بَقِيتُ&lt;/ar&gt;
 &lt;p&gt;আব্দুল্লাহ ইবনু কা'ব ইবনু মালেক (রাঃ) হতে বর্ণিত, তিনি বলেন, তখন তিনি আমাকে জিজ্ঞাসা করলেন, কী কারণে তুমি ('তাবুক' যুদ্ধে) অংশগ্রহণ করলে না? 'তুমি কি যানবাহন ক্রয় করনি? তখন আমি বললাম, হ্যাঁ, করেছি। আল্লাহর কসম! এ কথা সুনিশ্চিত যে, আমি যদি আপনি ব্যতীত দুনিয়ার অন্য কোন ব্যক্তির সামনে বসতাম, তাহলে আমি তার অসন্তুষ্টিকে ওযর-আপত্তি পেশ করে ঠাণ্ডা করার চেষ্টা করতাম। আর আমি তর্কে পটু। কিন্তু আল্লাহর কসম!&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;আমি বিশ্বাস করি যে, আজ যদি আমি আপনার কাছে মিথ্যা কথা বলে আমার প্রতি আপনাকে সন্তুষ্ট করার চেষ্টা করি, তাহলে শীঘ্রই আল্লাহ তাআলা আপনাকে আমার প্রতি অসন্তুষ্ট করে দিতে পারেন। আর যদি আপনার কাছে সত্য প্রকাশ করি, যদিও আপনি আমার প্রতি অসন্তুষ্ট হন, তবুও অবশ্যই আমি এতে আল্লাহর ক্ষমা পাওয়ার আশা করি। আল্লাহর কসম! আমার কোন ওযর ছিল না। আল্লাহর কসম!&lt;/p&gt;
-&lt;p&gt;সেই যুদ্ধে আপনার সঙ্গে না যাওয়ার সময় আমি সর্বাপেক্ষা শক্তিশালী ও সামর্থ্যবান ছিলাম। তখন রাসূলুল্লাহ (ﷺ) বললেন, 'সে সত্য কথাই বলেছে। তুমি এখন চলে যাও, যতদিন না তোমার সম্পর্কে আল্লাহ তাআলা ফয়সালা করে দেন'। তাই আমি উঠে চলে গেলাম...। ...এভাবে নবী (ﷺ) যখন থেকে আমাদের সঙ্গে কথা বলতে নিষেধ করেন, তখন থেকে পঞ্চাশ রাত পূর্ণ হলো। (উল্লেখ্য যে, কা'ব ইবনু মালিক, মুরারাহ ইবনু রাবী'আহ ও হিলাল ইবনু উমায়্যাহ (রাঃ) 'তাবুক' যুদ্ধে অংশগ্রহণ করা থেকে পিছনে থেকে যাওয়ার কারণে তাদের সম্পর্কে আল্লাহ তাআলার ফয়সালা না আসা পর্যন্ত সকল মুসলিম থেকে এমন কি তাদের স্ত্রীদের থেকেও ৫০ দিন বিরত থাকতে হয়েছিল)।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;এরপর আমি পঞ্চাশতম রাত শেষে ফজরের ছালাত আদায় করলাম এবং আমাদের এক ঘরের ছাদে এমন অবস্থায় বসে ছিলাম, যে অবস্থার ব্যাপারে আল্লাহ তাআলা (কুরআন মাজীদে) বর্ণনা করেছেন। আল্লাহ তাআলা বলেন, 'আল্লাহ অনুগ্রহ করেছেন নবীর প্রতি, এবং মুহাজির ও আনসারদের প্রতি যাঁরা সংকটকালে তাকে অনুসরণ করেছিল। এমনকি তাদের মধ্যে কিছু লোকের অন্তর বেঁকে যাওয়ার উপক্রম হওয়ার পরেও আল্লাহ তাদেরকে ক্ষমা করে দিয়েছিলেন। তিনি তাদের প্রতি বড়ই স্নেহশীল, বড়ই দয়ালু (আত-তওবা ১১৭)।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;'আর (তিনি অনুগ্রহ করলেন) ঐ তিনজনের প্রতিও যারা ('তাবুক' যুদ্ধে অংশগ্রহণ করা থেকে) পিছনে থেকে গিয়েছিল তাদের নাম হলো, কা'ব ইবনু মালিক, মুরারাহ ইবনু রাবী'আহ ও হিলাল ইবনু উমায়্যাহ (রাঃ)। তারা অনুশোচনার আগুনে এমনি দগ্ধীভূত হয়েছিলেন যে, শেষ পর্যন্ত পৃথিবী তার পূর্ণ বিস্তৃতি নিয়েও তাদের প্রতি সংকুচিত হয়ে গিয়েছিল। আর তাদের জীবন দুর্বিষহ হয়ে উঠল। আর তারা বুঝতে পারল যে, আল্লাহ ছাড়া তাদের কোন আশ্রয়স্থল নেই, তাঁর পথে ফিরে যাওয়া ব্যতীত। অতঃপর তিনি তাদের প্রতি অনুগ্রহ করলেন, যাতে তারা অনুশোচনায় তার দিকে ফিরে আসে। আল্লাহ অতিশয় তওবা কবুলকারী, বড়ই দয়ালু' (আত-তওবা, ১১৮)।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;'ওহে বিশ্বাসীগণ! তোমরা আল্লাহকে ভয় করো এবং সত্যপন্থীদের অন্তর্ভুক্ত হও' (আত-তওবা, ১১৯)। আমার জান-প্রাণ দুর্বিষহ এবং গোটা জগৎটা যেন আমার জন্য প্রশস্ত হওয়া সত্ত্বেও সংকীর্ণ হয়ে গিয়েছিল। এমন সময় শুনতে পেলাম এক চিৎকারকারীর চিৎকার। সে 'সালা' নামক পর্বতের উপর চড়ে উচ্চৈঃস্বরে ঘোষণা করছে, 'হে কা'ব ইবনু মালিক! সুসংবাদ গ্রহণ করুন'।&lt;/p&gt;
+&lt;p&gt;সেই যুদ্ধে আপনার সঙ্গে না যাওয়ার সময় আমি সর্বাপেক্ষা শক্তিশালী ও সামর্থ্যবান ছিলাম। তখন রাসূলুল্লাহ (ﷺ) বললেন, 'সে সত্য কথাই বলেছে। তুমি এখন চলে যাও, যতদিন না তোমার সম্পর্কে আল্লাহ তাআলা ফয়সালা করে দেন'। তাই আমি উঠে চলে গেলাম...। ...এভাবে নবী (ﷺ) যখন থেকে আমাদের সঙ্গে কথা বলতে নিষেধ করেন, তখন থেকে পঞ্চাশ রাত পূর্ণ হলো। (উল্লেখ্য যে, কা'ব ইবনু মালিক, মুরারাহ ইবনু রাবী'আহ ও হিলাল ইবনু উমায়্যাহ (রাঃ) 'তাবুক' যুদ্ধে অংশগ্রহণ করা থেকে পিছনে থেকে যাওয়ার কারণে তাদের সম্পর্কে আল্লাহ তাআলার ফয়সালা না আসা পর্যন্ত সকল মুসলিম থেকে এমন কি তাদের স্ত্রীদের থেকেও ৫০ দিন বিরত থাকতে হয়েছিল)।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;এরপর আমি পঞ্চাশতম রাত শেষে ফজরের ছালাত আদায় করলাম এবং আমাদের এক ঘরের ছাদে এমন অবস্থায় বসে ছিলাম, যে অবস্থার ব্যাপারে আল্লাহ তাআলা (কুরআন মাজীদের) বর্ণনা করেছেন। আল্লাহ তাআলা বলেন, 'আল্লাহ অনুগ্রহ করেছেন নবীর প্রতি, এবং মুহাজির ও আনসারদের প্রতি যাঁরা সংকটকালে তাকে অনুসরণ করেছিল। এমনকি তাদের মধ্যে কিছু লোকের অন্তর বেঁকে যাওয়ার উপক্রম হওয়ার পরেও আল্লাহ তাদেরকে ক্ষমা করে দিয়েছিলেন। তিনি তাদের প্রতি বড়ই স্নেহশীল, বড়ই দয়ালু (আত-তওবা ১১৭)।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;'আর (তিনি অনুগ্রহ করলেন) ঐ তিনজনের প্রতিও যারা ('তাবুক' যুদ্ধে অংশগ্রহণ করা থেকে) পিছনে থেকে গিয়েছিল তাদের নাম হলো, কা'ব ইবনু মালিক, মুরারাহ ইবনু রাবী'আহ ও হিলাল ইবনু উমায়্যাহ (রাঃ)। তারা অনুশোচনার আগুনে এমনি দগ্ধীভূত হয়েছিলেন যে, শেষ পর্যন্ত পৃথিবী তার পূর্ণ বিস্তৃতি নিয়েও তাদের প্রতি সংকুচিত হয়ে গিয়েছিল। আর তাদের জীবন দুর্বিষহ হয়ে উঠল। আর তারা বুঝতে পারল যে, আল্লাহ ছাড়া তাদের কোন আশ্রয়স্থল নেই, তাঁর পথে ফিরে যাওয়া ব্যতীত। অতঃপর তিনি তাদের প্রতি অনুগ্রহ করলেন, যাতে তারা অনুশোচনায় তার দিকে ফিরে আসে। আল্লাহ অতিশয় তওবা কবুলকারী, বড়ই দয়ালু' (আত-তওবা, ১১৮)।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;'ওহে বিশ্বাসীগণ! তোমরা আল্লাহকে ভয় করো এবং সত্যপন্থীদের অন্তর্ভুক্ত হও' (আত-তওবা, ১১৯)। আমার জান-প্রাণ দুর্বিষহ এবং গোটা জগৎটা যেন আমার জন্য প্রশস্ত হওয়া সত্ত্বেও সংকীর্ণ হয়ে গিয়েছিল। এমন সময় শুনতে পেলাম এক চিৎকারকারীর চিৎকার। সে 'সালা' নামক পর্বতের উপর চড়ে উচ্চৈঃস্বরে ঘোষণা করছে, 'হে কা'ব ইবনু মালিক! সুসংবাদ গ্রহণ করুন'।&lt;/p&gt;
 &lt;p&gt;কা'ব (রাঃ) বলেন, 'এ শব্দ আমার কানে পৌঁছামাত্র আমি সিজদায় পড়ে গেলাম। আর আমি বুঝলাম যে, আমার সুদিন ও খুশির খবর এসেছে'। আমি আরয করলাম, হে আল্লাহর রাসূল! আল্লাহ তাআলা সত্য কথা বলার কারণে আমাকে রক্ষা করেছেন, তাই আমার তওবা কবুলের নিদর্শন ঠিক রাখতে, আমার বাকী জীবনে সত্য কথাই বলব। আল্লাহর কসম! যখন থেকে আমি এ সত্য বলার কথা রাসূলুল্লাহ (ﷺ)-এর কাছে জানিয়েছি, তখন থেকে আজ পর্যন্ত আমার জানা মতে কোন মুসলিমকে সত্য কথার বিনিময়ে এরূপ নিয়ামত আল্লাহ দান করেননি, যে নিয়ামত আমাকে দান করেছেন।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;কা'ব (রাঃ) বলেন, 'যে দিন রাসূলুল্লাহ (ﷺ)-এর সম্মুখে সত্য কথা বলেছি, সেদিন হতে আজ পর্যন্ত অন্তরে মিথ্যা বলার ইচ্ছাও করিনি। আমি আশা পোষণ করি যে, বাকী জীবনও আল্লাহ তাআলা আমাকে মিথ্যা থেকে রক্ষা করবেন' (ছহীহ বুখারী, হা/৪৪১৮)। উপরিউক্ত আলোচনা হতে প্রতীয়মান হয় যে, সত্য ও সততা মানব জীবনে একটি মহৎ গুণ। সত্য ও সততার কারণে সাময়িকভাবে পৃথিবী সংকুচিত হলেও তার ফলাফল অনেক অনেকগুণে সাফল্যজনক ও মর্যাদাপূর্ণ হয়।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="7">
+      <c r="A7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>নারী ও পুরুষের আদর্শ</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>পঞ্চম আদর্শ</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>&lt;div class="page-text"&gt;&lt;p&gt;ছবরকারী বা সত্যের পথে দৃঢ়তা প্রদর্শনকারী পুরুষ ও স্ত্রীলোক। 'ছবর'- এর আভিধানিক অর্থ হচ্ছে, নিজেকে বেঁধে রাখা, ধৈর্য ধারণ করা। এখানে এমন পুরুষ ও নারীকে বোঝানো হয়েছে, যারা বিপদে-আপদে আল্লাহর দ্বীন পালন ও তাঁর ইবাদত করতে গিয়ে সকল প্রকার দুঃখ কষ্ট অকাতরে সহ্য করে অটল হয়ে থাকে। শত বাঁধার মোকাবিলা করে দ্বীনের উপর অবিচল থাকে এবং কোনক্রমেই আদর্শচ্যুত হয় না। আল্লাহ তাআলা বলেন,&lt;/p&gt;
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>&lt;div class="page-text"&gt;&lt;p&gt;ছবরকারী বা সত্যের পথে দৃঢ়তা প্রদর্শনকারী পুরুষ ও স্ত্রীলোক। 'ছবর'- এর আভিধানিক অর্থ হচ্ছে, নিজেকে বেঁধে রাখা, ধৈর্য ধারণ করা। এখানে এমন পুরুষ ও নারীকে বোঝানো হয়েছে, যারা বিপদে-আপদে আল্লাহর দ্বীন পালন ও তাঁর ইবাদত করতে গিয়ে সকল প্রকার দুঃখ কষ্ট অকাতরে সহ্য করে অটল হয়ে থাকে। শত বাঁধার মোক্কাবিলা করে দ্বীনের উপর অবিচল থাকে এবং কোনক্রমেই আদর্শচ্যুত হয় না। আল্লাহ তাআলা বলেন,&lt;/p&gt;
 &lt;ar&gt;سَلامٌ عَلَيْكُمْ بِمَا صَبَرْتُمْ فَنِعْمَ عُقْبَى الدَّارِ.&lt;/ar&gt;
 &lt;p&gt;'(ফেরেশতারা বলবে) 'তোমাদের ধৈর্যের কারণে তোমাদের উপর শান্তি বর্ষিত হোক। এবং তোমাদের এই পরিণাম গৃহ কতই না চমৎকার' (আর-রা'দ, ২৪)। আল্লাহ তাআলা অন্যত্র বলেন,&lt;/p&gt;
 &lt;ar&gt;وَجَزَاهُمْ بِمَا صَبَرُوا جَنَّةً وَحَرِيراً.&lt;/ar&gt;
 &lt;p&gt;'আর তাদের ধৈর্যের কারণে তাদের জন্য রয়েছে জান্নাত ও রেশমী পোশাক' (আদ-দাহার, ১২)।&lt;/p&gt;
 &lt;p&gt;আল্লাহ তাআলা অন্যত্র বলেন,&lt;/p&gt;
 &lt;ar&gt;وَاصْبِرْ نَفْسَكَ مَعَ الَّذِينَ يَدْعُونَ رَبَّهُمْ بِالْغَدَاةِ وَالْعَشِي.&lt;/ar&gt;
-&lt;p&gt;'আর আপনি নিজেকে ঐসব লোকের সাথে আঁকড়িয়ে ধরুন, যারা তাদের প্রতিপালককে সকাল-সন্ধ্যায় ডাকে' (আল-কাহাফ, ২৮)।&lt;/p&gt;
+&lt;p&gt;'আর আপনি নিজেকে ঐসব লোকের সাথে আঁকড়িয়ে ধরুন, যারা তাদের প্রতিপ্রতিপালককে সকাল-সন্ধ্যায় ডাকে' (আল-কাহাফ, ২৮)।&lt;/p&gt;
 &lt;p&gt;আল্লাহ তাআলা বলেন,&lt;/p&gt;
 &lt;ar&gt;فَاصْبِرْ عَلَى مَا يَقُولُونَ وَسَبِّحْ بِحَمْدِ رَبِّكَ قَبْلَ طُلُوعِ الشَّمْسِ وَقَبْلَ غُرُوبِهَا.&lt;/ar&gt;
 &lt;p&gt;'তারা যে সব দুঃখজনক ও কষ্টদায়ক কথা বলছে, সেসব কথাকে অকাতরে সহ্য করুন এবং সূর্যোদয়ের পূর্বে ও অস্ত যাওয়ার পরে আপনার প্রতিপালকের প্রশংসা সহকারে তাসবীহ পাঠ করুন' (ত্ব-হা, ১৩০)।&lt;/p&gt;
@@ -720,50 +766,50 @@
 &lt;ar&gt;يَا أَيُّهَا الَّذِينَ آمَنُوا اسْتَعِينُوا بِالصَّبْرِ وَالصَّلَاةِ إِنَّ اللَّهَ مَعَ الصَّابِرِينَ.&lt;/ar&gt;
 &lt;p&gt;'হে ঈমানদারগণ! তোমরা ধৈর্যসহকারে ছালাতের মাধ্যমে সাহায্য প্রার্থনা করো। নিশ্চয়ই আল্লাহ তাআলা ধৈর্যশীলদের সঙ্গে থাকেন' (আল-বাক্বারা, ১৫৩)।&lt;/p&gt;
 &lt;ar&gt;وَلَنَبْلُوَنَّكُمْ بِشَيْءٍ مِنَ الْخَوْفِ وَالْجُوعِ وَنَقْصٍ مِنَ الْأَمْوَالِ وَالْأَنْفُسِ وَالثَّمَرَاتِ وَبَشِّرِ الصَّابِرِينَ الَّذِينَ إِذَا أَصَابَتْهُمْ مُصِيبَةٌ قَالُوا إِنَّا لِلَّهِ وَإِنَّا إِلَيْهِ رَاجِعُونَ أُولَبِكَ عَلَيْهِمْ صَلَواتٌ مِنْ رَبِّهِمْ وَرَحْمَةٌ وَأُولَئِكَ هُمُ الْمُهْتَدُونَ.&lt;/ar&gt;
-&lt;p&gt;'আর অবশ্যই আমি তোমাদেরকে ভয়, ক্ষুধা, জান-মাল এবং ফল-ফলাদির ক্ষয়-ক্ষতি ইত্যাদি, যেকোনো কিছুর মাধ্যমে পরীক্ষা করব। হে নবী! আপনি ধৈর্যশীলদের সুসংবাদ দিয়ে দিন। (ধৈর্যশীল তারাই) যখন তাদের নিকটে কোন বিপদ আসে, তখন তারা বলে, 'নিশ্চয়ই আমরা আল্লাহর জন্য এবং আমরা আল্লাহর নিকটেই ফিরে যাব'। আর তাদের প্রতি রয়েছে তাদের প্রতিপালকের পক্ষ থেকে দয়া ও রহমত। আর এরাই হলো হেদায়াতপ্রাপ্ত ব্যক্তিগণ' (আল-বাক্বারা, ১৫৫-১৫৭)।&lt;/p&gt;
-&lt;p&gt;উপর্যুক্ত আয়াতগুলো দ্বারা শিক্ষণীয় বিষয়গুলো লক্ষনীয়: ১. শত্রু পক্ষের অত্যাচারের সময় একনিষ্ঠভাবে ধৈর্য ধারণ করতে হবে। তারা যে আচরণই করুক না কেন। ২. তারা বিভিন্ন কিছু বলে মান-সম্মানের হানি করলে, কিংবা কষ্ট দিলেও ধৈর্য ধারণ করতে হবে। যতক্ষণ পর্যন্ত ধৈর্য ধারণ করে কোন প্রতিবাদ না করা হবে, ততক্ষণ পর্যন্ত ধৈর্যধারণকারীর পক্ষে আল্লাহ তাআলার ফেরেশতা তার প্রতিবাদ করতে থাকেন। যেমন রাসূলুল্লাহ (ﷺ)-এর বাণী-&lt;/p&gt;
+&lt;p&gt;'আর অবশ্যই আমি তোমাদেরকে ভয়, ক্ষুধা, জান-মাল এবং ফল-ফলাদির ক্ষয়-ক্ষতি ইত্যাদি, যেকোনোমে কিছুর মাধ্যমে পরীক্ষা করব। হে নবী! আপনি ধৈর্যশীলদের সুসংবাদ দিয়ে দিন। (ধৈর্যশীল তারাই) যখন তাদের নিকটে কোন বিপদ আসে, তখন তারা বলে, 'নিশ্চয়ই আমরা আল্লাহর জন্য এবং আমরা আল্লাহর নিকটেই ফিরে যাব'। আর তাদের প্রতি রয়েছে তাদের প্রতিপালকের পক্ষ থেকে দয়া ও রহমত। আর এরাই হলো হেদায়াতপ্রাপ্ত ব্যক্তিগণ' (আল-বাক্বারা, ১৫৫-১৫৭)।&lt;/p&gt;
+&lt;p&gt;উপর্যুক্ত আয়াতগুলো দ্বারা শিক্ষণীয় বিষয়গুলো লক্ষনীয়: ১. শত্রু পক্ষের অত্যাচারের সময় একনিষ্ঠভাবে ধৈর্য ধারণ করতে হবে। তারা যে আচরণই করুক না কেন।&lt;br&gt;২. তারা বিভিন্ন কিছু বলে মান-সম্মানের হানি করলে, কিংবা কষ্ট দিলেও ধৈর্য ধারণ করতে হবে। যতক্ষণ পর্যন্ত ধৈর্য ধারণ করে কোন প্রতিবাদ না করা হবে, ততক্ষণ পর্যন্ত ধৈর্যধারণকারীর পক্ষে আল্লাহ তাআলার ফেরেশতা তার প্রতিবাদ করতে থাকেন। যেমন রাসূলুল্লাহ (ﷺ)-এর বাণী-&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ الله أَنَّ رَجُلًا شَتَمَ أَبَا بَكْرٍ، وَالنَّبِيُّ ﷺ جَالِسٌ يَتَعَجَّبُ وَيَتَبَسَّمُ، فَلَمَّا أَكْثَرَ رَدَّ عَلَيْهِ بَعْضَ قَوْلِهِ ، فَغَضِبَ النَّبِيُّ ، وَقَامَ فَلَحِقَهُ أَبُو بَكْرٍ، وَوقالَ : يَا رَسُولَ اللَّهِ! كَانَ يَشْتُمُنِي وَأَنْتَ جَالِسٌ ، فَلَمَّا رَدَدْتُ عَلَيْهِ بَعْضَ قَوْلِهِ غَضِبْتَ وَقُمْتَ. قَالَ : كَانَ مَعَكَ مَلَكٌ يَرُدُّ عَلَيْهِ، فَلَمَّا رَدَدْتَ عَلَيْهِ وَقَعَ الشَّيْطَانُ ". ثُمَّ قَالَ : " يَا أَبَا بَكْرٍ ثَلَاثُ كُلُّهُنَّ حَقٌّ مَا مِنْ عَبْدٍ ظُلِمَ بِمَظْلِمَةٍ فَيُغْضِي عَنْهَا لِلَّهِ إِلَّا أَعَزَّ اللَّهُ بِهَا نَصْرَهُ، وَمَا فَتَحَ رَجُلٌ بَابَ عَطِيَّةٍ يُرِيدُ بِهَا صِلَةً إِلَّا زَادَ اللَّهُ بِهَا كَثْرَةً، وَمَا فَتَحَ رَجُلٌ بَابَ مَسْأَلَةٍ يُرِيدُ بِهَا كَثْرَةً إِلَّا زَادَ اللَّهُ بِهَا قِلَّةٌ».&lt;/ar&gt;
 &lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, এক ব্যক্তি আবূ বকর (রাঃ)-কে গালি দিল। এ সময় রাসূলুল্লাহ (ﷺ) সেখানে বসা ছিলেন এবং আশ্চর্যান্বিত হয়ে মৃদু হাসলেন। লোকটি যখন বেশি গালি দিতে লাগল, তখন আবু বকর (রাঃ) তার কোন কোন কথার প্রতিবাদ করলেন। তাতে রাসূলুল্লাহ (ﷺ) রাগান্বিত হয়ে উঠে গেলেন। তখন আবূ বকর (রাঃ) তার পিছনে পিছনে গেলেন এবং বললেন, 'হে আল্লাহর রাসূল! লোকটি আমাকে গালি দিচ্ছিল, আর আপনি সেখানে বসা ছিলেন। আর আমি যখন তার কোন কোন কথার উত্তর দিলাম, তখন আপনি রাগ করে উঠে আসলেন'।&lt;/p&gt;
-&lt;p&gt;তিনি বললেন, 'তোমার সাথে এক জন ফেরেশতা ছিলেন, যিনি ঐ লোকটির কথার জবাব দিচ্ছিলেন। আর যখন তুমি নিজেই উত্তর দিতে লাগলে, তখন তোমার মাঝে শয়তান ঢুকে গেল'। অতঃপর রাসূলুল্লাহ (ﷺ) বললেন, 'হে আবূ বকর! এমন তিনটি বিষয় আছে যে, উহার প্রত্যেকটি অকাট্য সত্য। ১. যেই বান্দার উপর কোন প্রকার যুলুম করা হয়, আর সে আল্লাহর সন্তুষ্টির উদ্দেশ্যে তার কোনই প্রতিবাদ করে না, আল্লাহ তাআলা তার সম্মান বৃদ্ধি করেন এবং তাকে সাহায্য করেন।&lt;/p&gt;
-&lt;p&gt;২. যে ব্যক্তি তার আত্মীয়-স্বজনদের সাহায্যের উদ্দেশ্যে দানের দ্বার উন্মুক্ত করে দেয়, আল্লাহ তাআলা তার ধন-সম্পদ আরো বৃদ্ধি করে দেন। ৩. যে ব্যক্তি সম্পদ বৃদ্ধির আশায় ভিক্ষার দ্বার উন্মুক্ত করে দেয়, আল্লাহ তাআলা তার সম্পদ আরও কমিয়ে দেন' (মুসনাদে আহমাদ, হা/৯৬২২, ৯৮৭৪; মিশকাত, হা/৫১০২; সিলসিলা ছহীহা, হা/২২৩১)।&lt;/p&gt;
+&lt;p&gt;তিনি বললেন, 'তোমার সাথে এক জন ফেরেশতা ছিলেন, যিনি ঐ লোকটির কথার জবাব দিচ্ছিলেন। আর যখন তুমি নিজেই উত্তর দিতে লাগলে, তখন তোমার মাঝে শয়তান ঢুকে গেল'। অতঃপর রাসূলুল্লাহ (ﷺ) বললেন, 'হে আবূ বকর! এমন তিনটি বিষয় আছে যে, উহার প্রত্যেকটি অকাট্য সত্য।&lt;br&gt;১. যেই বান্দার উপর কোন প্রকার যুলুম করা হয়, আর সে আল্লাহর সন্তুষ্টির উদ্দেশ্যে তার কোনই প্রতিবাদ করে না, আল্লাহ তাআলা তার সম্মান বৃদ্ধি করেন এবং তাকে সাহায্য করেন।&lt;/p&gt;
+&lt;p&gt;২. যে ব্যক্তি তার আত্মীয়-স্বজনদের সাহায্যের উদ্দেশ্যে দানের দ্বার উন্মুক্ত করে দেয়, আল্লাহ তাআলা তার ধন-সম্পদ আরো বৃদ্ধি করে দেন।&lt;br&gt;৩. যে ব্যক্তি সম্পদ বৃদ্ধির আশায় ভিক্ষার দ্বার উন্মুক্ত করে দেয়, আল্লাহ তাআলা তার সম্পদ আরও কমিয়ে দেন' (মুসনাদে আহমাদ, হা/৯৬২২, ৯৮৭৪; মিশকাত, হা/৫১০২; সিলসিলা ছহীহা, হা/২২৩১)।&lt;/p&gt;
 &lt;p&gt;অন্য এক বর্ণনায় আছে,&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ أَنَّ رَجُلًا قَالَ : يَا رَسُولَ اللَّهِ! إِنَّ لِي قَرَابَةً أَصِلُهُمْ وَيَقْطَعُونِي، وَأُحْسِنُ إِلَيْهِمْ وَيُسِيئُونَ إِلَيَّ، وَأَحْلُمُ عَنْهُمْ وَيَجْهَلُونَ عَلَيَّ فَقَالَ : لَئِنْ كُنْتَ كَمَا قُلْتَ فَكَأَنَّمَا تُسِفُهُمُ الْمَلَّ، وَلَا يَزَالُ مَعَكَ مِنَ اللَّهِ ظَهِيرُ عَلَيْهِمْ مَا دُمْتَ عَلَى ذَلِكَ» .&lt;/ar&gt;
 &lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, একদা এক ব্যক্তি বলল, 'হে আল্লাহর রাসূল (ﷺ)! আমার এমন কতিপয় আত্মীয়-স্বজন আছে, আমি তাদের সাথে সদাচরণ করি। কিন্তু তারা আমার সাথে সম্পর্ক ছিন্ন করে। আমি তাদের সাথে সদ্ব্যবহার করি, অথচ তারা আমার সাথে দুর্ব্যবহার করে। আমি তাদের ব্যবহারে ধৈর্যধারণ করি, কিন্তু তারা আমার সাথে মূর্খতা প্রদর্শন করে'। উত্তরে রাসূলুল্লাহ (ﷺ) বললেন, 'তুমি যেরূপ বললে, যদি তুমি এরূপ আচরণই করে থাক, তাহলে তুমি তাদের মুখের উপর গরম ছাই নিক্ষেপ করছ। আর তুমি যতক্ষণ এই নীতির উপর বহাল থাকবে, ততক্ষণ পর্যন্ত আল্লাহর পক্ষ থেকে এক জন সাহায্যকারী থাকবেন, যিনি তাদের ক্ষতিকে প্রতিরোধ করবেন' (ছহীহ মুসলিম, হা/৬৬৮৯; মুসনাদে আহমাদ, হা/৯৩৩২; মিশকাত, হা/৪৯২৪)।&lt;/p&gt;
-&lt;p&gt;উপর্যুক্ত হাদীছ দুটি দ্বারা বুঝা যায় যে, ১. বিবাদীর মোকাবেলায় প্রতিবাদ না করে ধৈর্যধারণ করলে, আল্লাহর পক্ষ হতে এক জন সাহায্যকারী ফেরেশতা থাকেন। যিনি তার প্রতিবাদ করেন, তাদের ক্ষতি হতে সাহায্য করেন এবং আল্লাহ তার মান-মর্যাদা বৃদ্ধি করে দেন। ২. তারা যত দুরাচরণ করুক না কেন, তাদের প্রতিবাদে দুরাচরণ না করে তাদের সাথে ভদ্রতা বজায় রেখে, তাদের থেকে দূরে থাকতে হবে। ৩. মহান আল্লাহ তাআলা শুধু ধৈর্যধারণ নয়, উত্তম ধৈর্যধারণ করতে বলেছেন।&lt;/p&gt;
+&lt;p&gt;উপর্যুক্ত হাদীছ দুটি দ্বারা বুঝা যায় যে,&lt;br&gt;১. বিবাদীর মোক্কাবেলায় প্রতিবাদ না করে ধৈর্যধারণ করলে, আল্লাহর পক্ষ হতে এক জন সাহায্যকারী ফেরেশতা থাকেন। যিনি তার প্রতিবাদ করেন, তাদের ক্ষতি হতে সাহায্য করেন এবং আল্লাহ তার মান-মর্যাদা বৃদ্ধি করে দেন।&lt;br&gt;২. তারা যত দুরাচরণ করুক না কেন, তাদের প্রতিবাদে দুরাচরণ না করে তাদের সাথে ভদ্রতা বজায় রেখে, তাদের থেকে দূরে থাকতে হবে।&lt;br&gt;৩. মহান আল্লাহ তাআলা শুধু ধৈর্যধারণ নয়, উত্তম ধৈর্যধারণ করতে বলেছেন।&lt;/p&gt;
 &lt;br&gt;&lt;br&gt;
-&lt;p&gt;৪. ধৈর্যসহকারে বিপদে-আপদে দৃঢ় থাকতে নির্দেশ দিয়েছেন এবং পারস্পরিক বন্ধনকে আরও মজবুত করতে বলেছেন। ৫. ধৈর্যধারণের সাথে সাথে আল্লাহ তাআলাকেও ভয় করতে হবে। তাহলেই ইহকালে ও পরকালে সকল বিষয়ে সফল হওয়া যাবে। ৬. সূরা আসরে আল্লাহ রব্বুল আলামীন শপথ করে বললেন যে, 'মানুষ ক্ষতিগ্রস্ত'। এ কথা বলে তিনি চার শ্রেণির মানুষকে ক্ষতি হতে পৃথক করলেন। তারা হলো, ক. ঈমানদার বা মু'মিনগণ খ. যারা আল্লাহর সন্তুষ্টির উদ্দেশ্যে সৎকর্ম করে,&lt;/p&gt;
+&lt;p&gt;৪. ধৈর্যসহকারে বিপদে-আপদে দৃঢ় থাকতে নির্দেশ দিয়েছেন এবং পারস্পরিক বন্ধনকে আরও মজবুত করতে বলেছেন।&lt;br&gt;৫. ধৈর্যধারণের সাথে সাথে আল্লাহ তাআলাকেও ভয় করতে হবে। তাহলেই ইহকালে ও পরকালে সকল বিষয়ে সফল হওয়া যাবে।&lt;br&gt;৬. সূরা আসরে আল্লাহ রব্বুল আলামীন শপথ করে বললেন যে, 'মানুষ ক্ষতিগ্রস্ত'। এ কথা বলে তিনি চার শ্রেণির মানুষকে ক্ষতি হতে পৃথক করলেন। তারা হলো,&lt;br&gt;ক. ঈমানদার বা মু'মিনগণ&lt;br&gt;খ. যারা আল্লাহর সন্তুষ্টির উদ্দেশ্যে সৎকর্ম করে,&lt;/p&gt;
 &lt;br&gt;&lt;br&gt;
-&lt;p&gt;গ. যারা সত্যের উপদেশ দেয় এবং সত্য অবলম্বন করে ঘ. যারা ধৈর্যধারণের উপদেশ দেয় এবং ধৈর্যধারণ করে। ৭. আল্লাহ তাআলা ঈমানদারগণকে বিশেষভাবে ধৈর্যধারণের নির্দেশ দেন এবং উৎসাহ দেন যে, স্বয়ং আল্লাহ তাআলা ধৈর্যশীলদের সাথে থাকেন। ৮. মহান আল্লাহ তাআলা বলেন, তোমরা ধৈর্যসহ ছালাতের মাধ্যমে সাহায্য প্রার্থনা করো। নিশ্চয় এই ছালাত বিনয়ী ব্যক্তি ব্যতীত অন্যদের জন্য অতীব কঠিন একটি বিষয়।&lt;/p&gt;
+&lt;p&gt;গ. যারা সত্যের উপদেশ দেয় এবং সত্য অবলম্বন করে&lt;br&gt;ঘ. যারা ধৈর্যধারণের উপদেশ দেয় এবং ধৈর্যধারণ করে।&lt;br&gt;৭. আল্লাহ তাআলা ঈমানদারগণকে বিশেষভাবে ধৈর্যধারণের নির্দেশ দেন এবং উৎসাহ দেন যে, স্বয়ং আল্লাহ তাআলা ধৈর্যশীলদের সাথে থাকেন।&lt;br&gt;৮. মহান আল্লাহ তাআলা বলেন, তোমরা ধৈর্যসহ ছালাতের মাধ্যমে সাহায্য প্রার্থনা করো। নিশ্চয় এই ছালাত বিনয়ী ব্যক্তি ব্যতীত অন্যদের জন্য অতীব কঠিন একটি বিষয়।&lt;/p&gt;
 &lt;br&gt;&lt;br&gt;
-&lt;p&gt;৯. মহান আল্লাহ বলেন, আমি তোমাদেরকে বিভিন্নভাবে পরীক্ষা করব। যেমন: ভয়-ভীতি, দুঃখ-কষ্ট, ক্ষুধা, মাল-সম্পদ ও জীবনের ক্ষতি এবং ফসল, ফল-ফলাদির ক্ষতি দিয়ে পরীক্ষা করব। কিন্তু তোমাদেরকে ধৈর্যধারণ করতে হবে। ১০. এরকম বিপদের সময় যারা ধৈর্যধারণ করে বলে, إِنَّا لِلَّهِ وَإِنَّا إِلَيْهِ رَاجِعُونَ তাদের জন্য রয়েছে সুসংবাদ, আল্লাহর পক্ষ হতে অনুগ্রহ, করুণা ও হেদায়াত। অর্থাৎ, তারা ইহকালে ও পরকালে হবে সফলকামী।&lt;/p&gt;
+&lt;p&gt;৯. মহান আল্লাহ বলেন, আমি তোমাদেরকে বিভিন্নভাবে পরীক্ষা করব। যেমন: ভয়-ভীতি, দুঃখ-কষ্ট, ক্ষুধা, মাল-সম্পদ ও জীবনের ক্ষতি এবং ফসল, ফল-ফলাদির ক্ষতি দিয়ে পরীক্ষা করব। কিন্তু তোমাদেরকে ধৈর্যধারণ করতে হবে।&lt;br&gt;১০. এরকম বিপদের সময় যারা ধৈর্যধারণ করে বলে,&lt;br&gt;إِنَّا لِلَّهِ وَإِنَّا إِلَيْهِ رَاجِعُونَ&lt;br&gt;তাদের জন্য রয়েছে সুসংবাদ, আল্লাহর পক্ষ হতে অনুগ্রহ, করুণা ও হেদায়াত। অর্থাৎ, তারা ইহকালে ও পরকালে হবে সফলকামী।&lt;/p&gt;
 &lt;br&gt;&lt;br&gt;
-&lt;p&gt;উপর্যুক্ত আলোচনা হতে এটাই বুঝা গেল যে, সর্ব ক্ষেত্রে ধৈর্যধারণ করতে হবে। তাহলে তার বিনিময় অফুরন্ত। ধৈর্যের ব্যাপারে পবিত্র কুরআন মাজীদে আরও বহু আয়াত রয়েছে। এ ছাড়াও রাসূলুল্লাহ (ﷺ) ধৈর্যের ব্যাপারে যা বলেন,&lt;/p&gt;
+&lt;p&gt;উপর্যুক্ত আলোচনা হতে এটাই বুঝা গেল যে, সর্ব ক্ষেত্রে ধৈর্যধারণ করতে হবে। তাহলে তার বিনিময় অফুরন্ত। ধৈর্যের ব্যাপারে পবিত্র কোরআন মাজীদে আরও বহু আয়াত রয়েছে। এ ছাড়াও রাসূলুল্লাহ (ﷺ) ধৈর্যের ব্যাপারে যা বলেন,&lt;/p&gt;
 &lt;ar&gt;عَنْ سُلَيْمَانَ بْنِ صُرَدٍ قَالَ : قَالَ رَسُولُ اللَّهِ ﷺ : وَمَنْ قَتَلَهُ بَطْنُهُ لَمْ يُعَذَّبْ فِي قَبْرِهِ».&lt;/ar&gt;
 &lt;p&gt;সুলায়মান ইবনু ছুরাদ (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যাকে তার পেটের রোগ হত্যা করেছে, তাকে কবরে শাস্তি দেওয়া হবে না' (তিরমিযী, হা/১০৬৪; নাসাঈ, হা/২০৫২; মুসনাদে আহমাদ, হা/১৮৩১১ 'হাদীছ ছহীহ')। এই হাদীছ দ্বারা বুঝা যায় যে, কোন ব্যক্তি পেটের কোন রোগের কারণে মারা গেলে, তার কবরের শাস্তি মাফ করে দেওয়া হবে।&lt;/p&gt;
 &lt;ar&gt;عَنْ شَدَّادِ بْنِ أَوْسٍ وَالصُّنَابِحِيَّ أَنَّهُمَا دَخَلَا عَلَى رَجُلٍ مَرِيضٍ يَعُودَانِهِ، فَقَالَا لَهُ كَيْفَ أَصْبَحْتَ؟ قَالَ : أَصْبَحْتُ بِنِعْمَةٍ. قَالَ شَدَّادُ : أَبْشِرْ بِكَفَّارَاتِ السَّيِّئَاتِ، وَحَطَّ الْخَطَايَا : فَإِنِّي سَمِعْتُ رَسُولَ اللَّهِ ﷺ يَقُولُ : «إِنَّ اللَّهَ يَقُولُ : إِذَا أَنَا ابْتَلَيْتُ عَبْدًا مِنْ عِبَادِي مُؤْمِنًا، فَحَمِدَنِي عَلَى مَا ابْتَلَيْتُهُ، فَإِنَّهُ يَقُومُ مِنْ مَضْجَعِهِ ذَلِكَ كَيَوْمٍ وَلَدَتْهُ أُمُّهُ مِنَ الْخَطَايَا، وَيَقُولُ الرَّبُّ : أَنَا قَيَّدْتُ عَبْدِي وَابْتَلَيْتُهُ، فَأَجْرُوا لَهُ مَا كُنْتُمْ تُجْرُونَ لَهُ وَهُوَ صَحِيحٌ.&lt;/ar&gt;
-&lt;p&gt;শাদ্দাদ ইবনু আওস ও ছুনাবিহী (রাঃ) হতে বর্ণিত, তাঁরা উভয়ে এক পীড়িত ব্যক্তিকে দেখতে গেলেন এবং তাকে জিজ্ঞাসা করলেন, আজ সকাল কেমন হয়েছে? সে বলল, 'আল্লাহর দয়ায় ভাল হয়েছে'। এটা শুনে শাদ্দাদ বললেন, তোমার গুনাহ মাফ এবং অপরাধ মার্জনার সুসংবাদ গ্রহণ করো। কারণ আমি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছি, 'আল্লাহ তাআলা বলেন, আমি যখন আমার বান্দাদের মধ্যে কোনো মু'মিন বান্দাকে রোগগ্রস্ত করি, আর আমার এ রোগগ্রস্ত করা সত্ত্বেও সে আমার শুকরিয়া আদায় করে,&lt;/p&gt;
+&lt;p&gt;শাদ্দাদ ইবনু আওস ও ছুনাবিহী (রাঃ) হতে বর্ণিত, তাঁরা উভয়ে এক পীড়িত ব্যক্তিকে দেখতে গেলেন এবং তাকে জিজ্ঞাসা করলেন, আজ সকাল কেমন হয়েছে? সে বলল, 'আল্লাহর দয়ায় ভাল হয়েছে'। এটা শুনে শাদ্দাদ বললেন, তোমার গুনাহ মাফ এবং অপরাধ মার্জনার সুসংবাদ গ্রহণ করো। কারণ আমি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছি, 'আল্লাহ তাআলা বলেন, আমি যখন আমার বান্দাদের মধ্যেকোনো মু'মিন বান্দাকে রোগগ্রস্ত করি, আর আমার এ রোগগ্রস্ত করা সত্ত্বেও সে আমার শুকরিয়া আদায় করে,&lt;/p&gt;
 &lt;br&gt;&lt;br&gt;
 &lt;p&gt;তখন সে তার রোগ শয্যা হতে এমন নিষ্পাপ ও পবিত্র হয়ে উঠে, যেমন তার মা তাকে নিষ্পাপ ও পবিত্রাবস্থায় জন্ম দিয়েছিল'। আল্লাহ তাআলা আরো বলতে থাকেন, 'আমার বান্দাকে বন্ধ করে রেখেছি এবং রোগগ্রস্ত করে রেখেছি। অতএব (ফেরেশতা সকল) তোমরা তার সুস্থাবস্থায় যে নেকী লিখতেছিলে এই অবস্থায় তাই লিখতে থাক' (মুসনাদে আহমাদ, হা/১৭১৫৯; মিশকাত হা/১৫৭৯; 'হাদীছ ছহীহ')।&lt;/p&gt;
 &lt;p&gt;উপরিউক্ত হাদীছ দ্বারা বুঝা যায় যে, রোগগ্রস্ত হলে গুনাহ মুছে যায়। রোগগ্রস্ত হলেও আল্লাহর শুকরিয়া আদায় করতে হয়। আল্লাহ তাআলা মানুষকে রোগগ্রস্ত করে পরীক্ষা করেন। রোগগ্রস্ত হলে মানুষ এমন নিষ্পাপ হয়ে যায়, জন্মের সময় যেমন নিষ্পাপ থাকে। মানুষ সুস্থাবস্থায় যে নেকী অর্জন করে, অসুস্থ হলেও আল্লাহ তাআলা সে পরিমাণ নেকী লেখার জন্য ফেরেশতাদের আদেশ করেন।&lt;/p&gt;
 &lt;ar&gt;عَنْ سَعْدِ بْنِ أَبِي وَقَاصٍ قَالَ : قَالَ رَسُولُ اللهِ ﷺ : «عَجَبُ لِلْمُؤْمِنِ إِنْ أَصَابَهُ خَيْرٌ حَمِدَ وَشَكَرَ، وَإِنْ أَصَابَتْهُ مُصِيبَةٌ حَمِدَ اللهَ وَصَبَرَ ، وَالْمُؤْمِنُ يُؤْجَرُ فِي كُلِّ أَمْرِهِ حَتَّى فِي اللُّقْمَةِ يَرْفَعُهَا إِلَى فِي امْرَأَتِهِ».&lt;/ar&gt;
 &lt;p&gt;সা'দ ইবনু আবী ওয়াক্কাছ (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'মু'মিনদের জন্য খুশীর বিষয়, যদি তার প্রতি কোন কল্যাণ বর্তায় সে বলে, اَلْحَمْدُ للهِ বা আল্লাহর প্রশংসা করে। আর যদি কোন বিপদ আপতিত হয়, তবুও সে বলে اَلْحَمْدُ للهِ বা আল্লাহর প্রশংসা করে এবং ধৈর্যধারণ করে। সুতরাং মু'মিন তার প্রত্যেক কাজেই নেকী অর্জন করে। এমনকি স্ত্রীর মুখে খাদ্যের লোকমা তুলে দিলেও নেকী পায়' (বায়হাক্বী শুআবুল ঈমান, হা/৪১৬৮; মিশকাত, হা/১৭৩৩ 'হাদীছ ছহীহ')।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي مُوسَى الْأَشْعَرِيَّ الله قَالَ : قَالَ رَسُولُ اللهِ ﷺ : «إِذَا مَاتَ وَلَدُ الْعَبْدِ قَالَ اللَّهُ تَعَالَى لِمَلَائِكَتِهِ : قَبَضْتُمْ وَلَدَ عَبْدِي، فَيَقُولُونَ : نَعَمْ. فَيَقُولُ : قَبَضْتُمْ ثَمَرَةَ فُؤَادِهِ. فَيَقُولُونَ : نَعَمْ. فَيَقُولُ : مَاذَا قَالَ عَبْدِي؟ فَيَقُولُونَ : حَمِدَكَ وَاسْتَرْجَعَ فَيَقُولُ اللَّهُ : ابْنُوا لِعَبْدِي بَيْتًا في الْجَنَّةِ، وَسَمُوهُ بَيْتَ الْحَمْدِ».&lt;/ar&gt;
-&lt;p&gt;আবূ মূসা আল-আশ'আরী (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যখন কোন বান্দার সন্তান মারা যায়, আল্লাহ তাআলা তাঁর ফেরেশতাদের বলেন, তোমরা কি আমার বান্দার সন্তানকে উঠিয়ে নিলে? তারা বলে হ্যাঁ! আল্লাহ আবার জিজ্ঞাসা করেন, তোমরা কি তার অন্তরের ধনকে কেড়ে নিলে? তারা বলে হ্যাঁ! আল্লাহ আবার জিজ্ঞাসা করেন, তখন তারা কি বলল? ফেরেশতারা বলে, তখন তারা বলল إِنَّا للَّهِ وَإِنَّ إِلَيْهِ رَاجِعُونَ  الْحَمْدُ للهِ তখন আল্লাহ বলেন, 'আমার বান্দার জন্য জান্নাতে একটি ঘর নির্মাণ করো এবং তার নাম রাখ 'বায়তুল হামদ' (তিরমিযী, হা/১০২১; সিলসিলা ছহীহা, হা/৩২২৮, ১৪০৮)।&lt;/p&gt;
+&lt;p&gt;আবূ মূসা আল-আশ'আরী (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যখন কোন বান্দার সন্তান মারা যায়, আল্লাহ তাআলা তাঁর ফেরেশতাদের বলেন, তোমরা কি আমার বান্দার সন্তানকে উঠিয়ে নিলে? তারা বলে হ্যাঁ! আল্লাহ আবার জিজ্ঞাসা করেন, তোমরা কি তার অন্তরের ধনকে কেড়ে নিলে? তারা বলে হ্যাঁ! আল্লাহ আবার জিজ্ঞাসা করেন, তখন তারা কি বলল? ফেরেশতারা বলে, তখন তারা বলল&lt;br&gt;إِنَّا للَّهِ وَإِنَّ إِلَيْهِ رَاجِعُونَ  الْحَمْدُ للهِ&lt;br&gt;তখন আল্লাহ বলেন, 'আমার বান্দার জন্য জান্নাতে একটি ঘর নির্মাণ করো এবং তার নাম রাখ 'বায়তুল হামদ' (তিরমিযী, হা/১০২১; সিলসিলা ছহীহা, হা/৩২২৮, ১৪০৮)।&lt;/p&gt;
 &lt;p&gt;কোন ব্যক্তির ছেলে-মেয়ে মারা গেলে তার জন্য জরুরী কর্তব্য হচ্ছে, প্রথমে 'আলহামদুলিল্লাহ' এবং 'ইন্না-লিল্লাহি ওয়া ইন্না- ইলাইহি রাজিউন' বলা।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ اللهِ قَالَ : قَالَ رَسُولُ اللهِ هِ : إِنَّ الرَّجُلَ لَيَكُوْনُ لَهُ عِنْدَ اللَّهِ الْمَنْزِلَةُ فَمَا يَبْلُغُهَا بِعَمَلٍ فَمَا يَزالُ اللَّهُ يَبْتَلِيْهِ بِمَا يَكْرَهُ حَتَّى يَبْلُغَهُ إِيَّاهُ.&lt;/ar&gt;
 &lt;p&gt;আবূ হুরায়রা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'কোন মানুষ যখন আল্লাহর নিকট মর্যাদা সম্পন্ন স্থানের অধিকারী হয়ে যায় এবং সে আমলের মাধ্যমে সে স্থানে পৌঁছতে পারে না। তখন আল্লাহ তাকে সর্বদা এমন বিপদগ্রস্ত করে রাখেন, যা তার নিকট অপছন্দনীয়। তারপর আল্লাহ তাকে ঐ মর্যাদা সম্পন্ন স্থানে পৌঁছে দেন' (মুসনাদে আবী ইয়ালা, হা/৬০৯৫; ছহীহ ইবনু হিব্বান, হা/২৯০৮; সিলসিলা ছহীহা হা/৩২৪৮, ১৫৯৯)।&lt;/p&gt;
-&lt;p&gt;উপর্যুক্ত হাদীছগুলোতে কয়েকটি বিষয় লক্ষণীয়- ১. মানুষ যদি কঠিন হতে কঠিন বিপদের সময় এবং কঠিন হতে কঠিন রোগ যন্ত্রণায় ধৈর্য ধারণ করে ও আল-হামদু-লিল্লাহ বলে, তাহলে তার জন্য রয়েছে জান্নাত। ২. রোগে-শোকে ধৈর্যধারণ করে সে যদি সুস্থ হয়, তাহলে নিষ্পাপ অবস্থায় সুস্থ হয়। আর যদি মারা যায়, আল্লাহ তাকে মাফ করে দেন এবং জান্নাত নসীব করেন।&lt;/p&gt;
-&lt;p&gt;আবু দারদা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'কিয়ামতের দিন মু'মিনের মীযানের পাল্লায় সর্বাপেক্ষা ভারী যে জিনিস রাখা হবে, তা হলো উত্তম চরিত্র। আর আল্লাহ তাআলা কর্কশভাষী দুশ্চরিত্রকে ঘৃণা করেন' (তিরমিযী, হা/মিশকাত, হা/৪৮৫৯)।&lt;/p&gt;
-&lt;p&gt;উক্ত হাদীছ দ্বারা বুঝা যায় যে, কিয়ামতের দিন মীযানের পাল্লায় সবচেয়ে ভারি জিনিস হচ্ছে, সৎ চরিত্র। আর সৎ চরিত্রের মৌলিক গুণ হচ্ছে, সর্বাবস্থায় ধৈর্যধারণ করা। হে প্রতিপালক! তুমি আমাদের সকলকে সর্বাবস্থায় ধৈর্যধারণ করার তৌফিক দান করো এবং আমাদের সকলকে জান্নাত নসীব করো। আমীন!&lt;/p&gt;
+&lt;p&gt;উপর্যুক্ত হাদীছগুলোতে কয়েকটি বিষয় লক্ষণীয়-&lt;br&gt;১. মানুষ যদি কঠিন হতে কঠিন বিপদের সময় এবং কঠিন হতে কঠিন রোগ যন্ত্রণায় ধৈর্য ধারণ করে ও আল-হামদু-লিল্লাহ বলে, তাহলে তার জন্য রয়েছে জান্নাত।&lt;br&gt;২. রোগে-শোকে ধৈর্যধারণ করে সে যদি সুস্থ হয়, তাহলে নিষ্পাপ অবস্থায় সুস্থ হয়। আর যদি মারা যায়, আল্লাহ তাকে মাফ করে দেন এবং জান্নাত নসীব করেন।&lt;/p&gt;
+&lt;p&gt;আবু দারদা (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'কেয়ামতের দিন মু'মিনের মীযানের পাল্লায় সর্বাপেক্ষা ভারী যে জিনিস রাখা হবে, তা হলো উত্তম চরিত্র। আর আল্লাহ তাআলা কর্কশভাষী দুশ্চরিত্রকে ঘৃণা করেন' (তিরমিযী, হা/মিশকাত, হা/৪৮৫৯)।&lt;/p&gt;
+&lt;p&gt;উক্ত হাদীছ দ্বারা বুঝা যায় যে, কেয়ামতের দিন মীযানের পাল্লায় সবচেয়ে ভারি জিনিস হচ্ছে, সৎ চরিত্র। আর সৎ চরিত্রের মৌলিক গুণ হচ্ছে, সর্বাবস্থায় ধৈর্যধারণ করা। হে প্রতিপালক! তুমি আমাদের সকলকে সর্বাবস্থায় ধৈর্যধারণ করার তৌফিক দান করো এবং আমাদের সকলকে জান্নাত নসীব করো। আমীন!&lt;/p&gt;
 &lt;p&gt;আয়াতগুলোতে বিপদের সময়ে ধৈর্যধারণ করতে এবং সকাল-সন্ধ্যা আল্লাহকে ডাকার জন্য বলা হয়েছে, যা মু'মিন নারী-পুরুষের আদর্শ।&lt;/p&gt;
 &lt;ar&gt;عَنِ ابْنِ عُمَرَ أَنَّ مَوْلَاةً لَهُ أَتَتْهُ فَقَالَت : اشْتَدَّ عَلَى الزَّমَانُ وَإِنِّي أُرِيدُ أَنْ أَخْرُجَ إِلَى الْعِرَاقِ. قَالَ : فَهَلاً إِلَى الشَّأْمِ أَرْضِ الْمَنْشَرِ اصْبِرِى لَكَاعِ فَإِنِّي سَمِعْتُ رَسُولُ اللَّهِ ﷺ يَقُولُ : مَنْ صَبَرَ عَلَى شِدَّتِهَا وَلا وَائِهَا كُنْتُ لَهُ شَهِيدًا أَوْ شَفِيعًا يَوْمَ الْقِيَامَةِ ».&lt;/ar&gt;
-&lt;p&gt;ইবনু উমার (রাঃ) বর্ণনা করেছেন। তার এক মুক্ত দাসী এসে তাঁকে বললেন, আমার জন্য দিনাতিপাত কঠিন হয়ে পড়েছে। তাই আমি 'ইরাকের' দিকে যেতে চাই। তিনি বললেন, তবে তুমি 'সিরিয়ার' দিকে যাবার মনস্থ করলে না কেন? সেটা তো হাশরের মাঠ। তিনি আরও বললেন, আরে নির্বোধ? ধৈর্যধারণ করো। রাসূলুল্লাহ (ﷺ)-কে আমি বলতে শুনেছি, যে লোক মদীনার কষ্ট-কাঠিন্য ও দুর্ভিক্ষে ধৈর্যধারণ করে, কিয়ামতের দিন আমি তার জন্য সাক্ষী হব এবং সুপারিশকারী হব (তিরমিযী, হা/৩৯১৮)।&lt;/p&gt;
+&lt;p&gt;ইবনু উমর (রাঃ) বর্ণনা করেছেন। তার এক মুক্ত দাসী এসে তাঁকে বললেন, আমার জন্য দিনাতিপাত কঠিন হয়ে পড়েছে। তাই আমি 'ইরাকের' দিকে যেতে চাই। তিনি বললেন, তবে তুমি 'সিরিয়ার' দিকে যাবার মনস্থ করলে না কেন? সেটা তো হাশরের মাঠ। তিনি আরও বললেন, আরে নির্বোধ? ধৈর্যধারণ করো। রাসূলুল্লাহ (ﷺ)-কে আমি বলতে শুনেছি, যে লোক মদীনার কষ্ট-কাঠিন্য ও দুর্ভিক্ষে ধৈর্যধারণ করে, কেয়ামতের দিন আমি তার জন্য সাক্ষী হব এবং সুপারিশকারী হব (তিরমিযী, হা/৩৯১৮)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَنَسٍ اللهُ أَنَّ رَسُولَ اللهِ اللهِ قَالَ : ( مَنِ احْتَسَبَ ثَلَاثَةٌ مِنْ صُلْبِهِ دَخَلَ الْجَنَّةَ ». فَقَامَتِ امْرَأَةٌ فَقَالَتْ : أَوِ اثْنَانِ قَالَ : ( أَوِ اثْنَانِ ». قَالَتِ الْمَرْأَةُ : يَا لَيْتَنِي قُلْتُ وَاحِدًا.&lt;/ar&gt;
 &lt;p&gt;আনাস (রাঃ) হতে বর্ণিত, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে ব্যক্তি তার তিন সন্তানের মৃত্যুতে ধৈর্যসহ সওয়াবের আশা করবে, সে জান্নাতে প্রবেশ করবে। তখন এক মহিলা দাঁড়িয়ে বলল, যদি দুই সন্তানের উপর ধৈর্যধারণ করে থাকে? তিনি বললেন, দুই জন হলেও। তখন সেই মহিলা বলল, হায়! আমি যদি একজনের কথা বলতাম' (নাসাঈ, হা/১৮৭২; সিলসিলা ছহীহা, হা/২৩০২)।&lt;/p&gt;
 &lt;ar&gt;أَنَّ عَمْرَو بْنَ شُعَيْبٍ الله كَتَبَ إِلَى عَبْدِ اللهِ بْنِ عَبْدِ الرَّحْمَنِ بْنِ أَبِي حُسَيْنٍ يُعَজِّيهِ بِابْنٍ لَهُ هَلَكَ وَذَكَرَ فِي كِتَابِهِ أَنَّهُ سَمِعَ أَبَاهُ يُحَدِّثُ عَنْ جَدَّهِ عَبْدِ اللَّهِ بْنِ عَمْرِو بْنِ الْعَاصِ قَالَ قَالَ رَسُولُ اللهِ ﷺ : « إِنَّ اللَّهَ لَا يَرْضَى لِعَبْدِهِ الْمُؤْمِنِ إِذَا ذَهَبَ بِصَفِيِّهِ مِنْ أَهْلِ الْأَرْضِ فَصَبَرَ وَاحْتَسَبَ وَقَالَ مَا أُمِرَ بِهِ بِثَوَابِ دُونَ الْجَنَّةِ ».&lt;/ar&gt;
 &lt;p&gt;আমর ইবনু শু'আইব (রাঃ) আব্দুল্লাহ ইবনু আব্দুর রহমানের এক ছেলের মৃত্যুতে ধৈর্যধারণ করার জন্য তাঁর কাছে একটি চিঠি লিখেন। চিঠিতে তিনি উল্লেখ করেন যে, তিনি তাঁর পিতাকে তাঁর দাদা আব্দুল্লাহ ইবনু আমর ইবনুল আস (রাঃ) থেকে বর্ণনা করতে শুনেছেন। তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন যে, পৃথিবীর কোন প্রিয়জন মারা যাওয়ার পর যখন মু'মিন ব্যক্তি ধৈর্যধারণ করে এবং সওয়াবের আশা রাখে, তখন আল্লাহ তাআলা তার জন্য জান্নাত ছাড়া অন্য কোন সওয়াব দিয়ে সন্তুষ্ট হন না। অর্থাৎ, তার প্রতিদান হলো জান্নাত (নাসাঈ, হা/১৮৭১; সুনানে নাসাঈ, কুবরা, হা/১৯৯৮)।&lt;/p&gt;
 &lt;ar&gt;عَنِ ابْنِ عُمَرَ قَالَ : سَمِعْتُ رَسُولُ اللهِ ﷺ يَقُولُ : ( مَنْ صَبَرَ عَلَى لأُوَائِهَا كُنْتُ لَهُ شَفِيعًا أَوْ شَهِيدًا يَوْمَ الْقِيَامَةِ ».&lt;/ar&gt;
-&lt;p&gt;ইবনু উমার (রাঃ) বর্ণনা করেছেন। তিনি বলেন, আমি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছি, 'যে ব্যক্তি এখানকার দুঃখ কষ্ট সহ্য করে, আমি কিয়ামতের দিন অবশ্যই তার জন্য শাফা'আত করব অথবা তার পক্ষে সাক্ষী হব' (ছহীহ মুসলিম, হা/৩৪১০, ৩৪১২; মুসনাদে আহমাদ, হা/৬৪৪০)।&lt;/p&gt;
+&lt;p&gt;ইবনু উমর (রাঃ) বর্ণনা করেছেন। তিনি বলেন, আমি রাসূলুল্লাহ (ﷺ)-কে বলতে শুনেছি, 'যে ব্যক্তি এখানকার দুঃখ কষ্ট সহ্য করে, আমি কেয়ামতের দিন অবশ্যই তার জন্য শাফা'আত করব অথবা তার পক্ষে সাক্ষী হব' (ছহীহ মুসলিম, হা/৩৪১০, ৩৪১২; মুসনাদে আহমাদ, হা/৬৪৪০)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَنَسٍ الله قَالَ : مَرَّ النَّبِيُّ اللهِ بِامْرَأَةٍ تَبْكِي عِنْدَ قَبْرٍ، فَقَالَ : اتَّقِي اللَّهَ وَاصْبِرِي، قَالَتْ : إِلَيْكَ عَنِّي، فَإِنَّكَ لَمْ تُصَبْ بِمُصِيبَتِي، وَلَمْ تَعْرِفْهُ، فَقِيلَ لَهَا : إِنَّهُ النَّبِيُّ ﷺ فَأَتَتْ بَابَ النَّبِيِّ فَلَمْ تَجِدُ عِنْدَهُ بَوَّابِينَ. فَقَالَتْ : لَمْ أَعْرِفْكَ، فَقَالَ : إِنَّمَا الصَّبْرُ عِنْدَ الصَّدْمَةِ الْأُولَى».&lt;/ar&gt;
 &lt;p&gt;আনাস (রাঃ) হতে বর্ণিত, তিনি বলেন, নবী (ﷺ) এক মহিলার পাশ দিয়ে যাচ্ছিলেন, যিনি কবরের পার্শ্বে কাঁদছিলেন। নবী (ﷺ) বললেন, 'তুমি আল্লাহকে ভয় করো এবং ধৈর্যধারণ কর'। মহিলাটি বললেন, 'আমার নিকট থেকে দূর হন। আপনার উপর তো আমার মতো বিপদ উপস্থিত হয়নি'। তিনি নবী (ﷺ)-কে চিনতে পারেননি। পরে তাকে বলা হলো, তিনি তো আল্লাহ তাআলার নবী (ﷺ)। তখন তিনি নবী (ﷺ)-এর দরজায় উপস্থিত হলেন, এমতাবস্থায় তাঁর কাছে কোন প্রহরী ছিল না। তিনি নিবেদন করলেন, আমি আপনাকে চিনতে পারিনি। তিনি (নবী (ﷺ)) বললেন, 'বিপদের প্রথম অবস্থাতেই তো ধৈর্য (ধারণ করতে হয়)' (ছহীহ বুখারী, হা/১২৮৩; আবূ দাউদ, হা/৩১২৪; মিশকাত, হা/১৭২৮)। অর্থাৎ যেকোনো বিপদে পড়লে প্রথমেই ধৈর্যধারণ করা হলো পূর্ণ মু'মিনের বিশেষ বৈশিষ্ট্য।&lt;/p&gt;
 &lt;ar&gt;عَنْ صُهَيْبٍ ، قَالَ : قَالَ رَسُولُ اللهِ : ( عَجَبًا لأَمْرِ الْمُؤْمِنِ إِنَّ أَمْرَهُ كُلَّهُ خَيْرٌ وَلَيْسَ ذَاكَ لأَحَدٍ إِلا لِلْمُؤْمِنِ إِنْ أَصَابَتْهُ سَرَّاءُ شَكَرَ فَكَانَ خَيْرًا لَهُ وَإِنْ أَصَابَتْهُ ضَرَّاءُ صَبَرَ فَكَانَ خَيْرًا لَهُ ».&lt;/ar&gt;
@@ -773,26 +819,26 @@
 &lt;p&gt;উপরিউক্ত আলোচনা হতে এটাই প্রতীয়মান হয় যে, সুখে-দুঃখে, বালা, মছিবতে রোগ-যন্ত্রণায়, অত্যাচারীদের অত্যাচারে সর্বাবস্থায় ধৈর্যধারণ করাই প্রকৃত মু'মিনের কাজ। আর পরস্পরকে ধৈর্যধারণের উপদেশ দিতে হবে এবং নিজেদেরকেও ধৈর্যধারণ করতে হবে।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="8">
+      <c r="A8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>নারী ও পুরুষের আদর্শ</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>ষষ্ঠ আদর্শ</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;আল্লাহর নিকট বিনীত-নম্র পুরুষ ও স্ত্রীলোক। আল্লাহ তাআলা এখানে এমন নারী-পুরুষের আদর্শ বর্ণনা করেছেন, যারা অন্তর-মন ও অঙ্গ-প্রত্যঙ্গ সব কিছু দিয়ে বিনীতভাবে আল্লাহ তাআলার ইবাদত করে। এখানে এমন এক শব্দ উল্লিখিত হয়েছে যার অর্থ- প্রশান্তি, স্থিতি, প্রীতি, শ্রদ্ধা, ভক্তি, বিনয়, ভয় মিশ্রিত ভালোবাসা এবং আল্লাহ তাআলার প্রতি আগ্রহ, উৎসাহ। আল্লাহ তাআলা বলেন,&lt;/p&gt;
 &lt;ar&gt;قَدْ أَفْلَحَ الْمُؤْمِنُونَ الَّذِينَ هُمْ فِي صَلَاتِهِمْ خَاشِعُونَ.&lt;/ar&gt;
@@ -806,17 +852,16 @@
 &lt;ar&gt;يَعْلَمُ مَا بَيْنَ أَيْدِيهِمْ وَمَا خَلْفَهُمْ وَلَا يَشْفَعُونَ إِلَّا لِمَنِ ارْتَضَى وَهُمْ مِنْ خَشْيَتِهِ مُشْفِقُونَ.&lt;/ar&gt;
 &lt;p&gt;'তিনি (আল্লাহ তাআলা) তাদের বর্তমান ও ভবিষ্যত সম্পর্কে জানেন। তিনি যে সকল ব্যক্তির প্রতি খুবই সন্তুষ্ট, তারা শুধু সে সকল ব্যক্তি ছাড়া অন্য কারও জন্য সুপারিশ করে না। তারা তাঁর (আল্লাহ তাআলার) ভয়ে ভীত-সন্ত্রস্ত। অর্থাৎ বিনীত-নম্র ব্যক্তি' (আল-আম্বিয়া, ২৮)।&lt;/p&gt;
 &lt;ar&gt;فَاسْتَجَبْنَا لَهُ وَوَهَبْنَا لَهُ يَحْيَى وَأَصْلَحْنَا لَهُ زَوْجَهُ إِنَّهُمْ কَانُوا يُسَارِعُونَ فِي الْخَيْرَاتِ وَيَدْعُونَنَا رَغَبًا وَرَهَبًا وَكَانُوا لَنَا خَاشِعِينَ.&lt;/ar&gt;
-&lt;p&gt;'তখন আমি তাঁর (যাকারিয়া (আঃ)-এর) ডাকে সাড়া দিয়েছিলাম এবং তাঁকে দান করেছিলাম ইয়াহইয়া। আর তাঁর জন্যই তাঁর স্ত্রীর বন্ধ্যাত্ব দূর করে দিয়েছিলাম। কারণ এরা দ্রুতগতিতে সৎকর্ম বাস্তবায়ন করত এবং আমাকে (আল্লাহ তাআলাকে) ভয়-ভীতি সহকারে পূর্ণ আশা নিয়ে ডাকত। কারণ তাঁরা আমার ভয়ে ভীত ছিল। অর্থাৎ বিনয়ী ছিল' (আল-আম্বিয়া, ৯০)।&lt;/p&gt;
+&lt;p&gt;'তখন আমি তাঁর (যাকারিয়া (আঃ)-এর) ডাকে সাড়া দিয়েছিলাম এবং তাঁকে দান করেছিলাম ইয়াহিয়া। আর তাঁর জন্যই তাঁর স্ত্রীর বন্ধ্যাত্ব দূর করে দিয়েছিলাম। কারণ এরা দ্রুতগতিতে সৎকর্ম বাস্তবায়ন করত এবং আমাকে (আল্লাহ তাআলাকে) ভয়-ভীতি সহকারে পূর্ণ আশা নিয়ে ডাকত। কারণ তাঁরা আমার ভয়ে ভীত ছিল। অর্থাৎ বিনয়ী ছিল' (আল-আম্বিয়া, ৯০)।&lt;/p&gt;
 &lt;ar&gt;مَنْ خَشِيَ الرَّحْمَنَ بِالْغَيْبِ وَجَاءَ بِقَلْبٍ مُنِيبٍ.&lt;/ar&gt;
 &lt;p&gt;'জান্নাতকে ঐ ব্যক্তির জন্য নিকটে করা হবে, যে ব্যক্তি দয়াময় (আল্লাহ তাআলাকে) না দেখেই ভয় করত এবং (আল্লাহ তাআলার) নির্দেশ পালনের জন্য বিনয়ে অবনত মন নিয়ে উপস্থিত হতো' (আল-ক্বাফ, ৩৩)।&lt;/p&gt;
 &lt;ar&gt;وَلِمَنْ خَافَ مَقَامَ رَبِّهِ جَنَّتَانِ.&lt;/ar&gt;
 &lt;p&gt;'যে ব্যক্তি তার প্রতিপালকের সামনে উপস্থিত হওয়ার ভয় করে, তার জন্য রয়েছে দুটি জান্নাত' (আর-রহমান, ৪৬)।&lt;/p&gt;
-&lt;p&gt;উপরোক্ত আয়াতগুলোতে কয়েকটি বিষয় বিষেশভাবে লক্ষণীয়:&lt;/p&gt;
-&lt;p&gt;১. যারা বিশেষভাবে আল্লাহ তাআলার ভয়ে অবনত থাকে, তারা পরকালে লাভবান।&lt;/p&gt;
+&lt;p&gt;উপরোক্ত আয়াতগুলোতে কয়েকটি বিষয় বিষেশভাবে লক্ষণীয়: ১. যারা বিশেষভাবে আল্লাহ তাআলার ভয়ে অবনত থাকে, তারা পরকালে লাভবান।&lt;/p&gt;
 &lt;p&gt;২. যারা আল্লাহ তাআলাকে ভয় করে, আল্লাহ তাআলা তাদের প্রতি সন্তুষ্ট থাকেন।&lt;/p&gt;
 &lt;p&gt;৩. যারা আল্লাহ তাআলার ভয়ে অবনত, তাদের জন্য রয়েছে মহা পুরস্কার চিরস্থায়ী শান্তির জায়গা জান্নাত।&lt;/p&gt;
 &lt;ar&gt;عَنْ عُثْمَانَ اللهِ قَالَ : قَالَ رَسُولُ اللهِ : «مَا مِنَ امْرِئٍ مُسْلِمٍ تَحْضُرُهُ صَلَاةً مَكْتُوبَةٌ فَيُحْسِنُ وُضُوءَهَا وَخُشُوعَهَا وَرُكُوعَهَا، إِلَّا كَانَتْ كَفَّارَةً لِمَا قَبْلَهَا مِنَ الذُّنُوبِ مَا لَمْ يُؤْتِ كَبِيرَةً، وَذَلِكَ الدَّهْرَ كُلَّهُ».&lt;/ar&gt;
-&lt;p&gt;উসমান (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে মুসলিম ফরয ছালাতের সময় হলে উত্তমভাবে অযু করে, বিনয় ও ভয়-ভীতি সহকারে রুকু করে। অর্থাৎ ছালাত আদায় করে (তার এ ছালাত), পূর্বের গুনাহের কাফফারা (প্রায়শ্চিত্ত) হয়ে যায়, যতক্ষণ না সে কাবীরা গুনাহ করে থাকে। আর এভাবে সর্বদাই চলতে থাকবে' (ছহীহ মুসলিম, হা/২২৮; মিশকাত, হা/২৮৬)।&lt;/p&gt;
+&lt;p&gt;উসমান (রাঃ) হতে বর্ণিত, তিনি বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'যে মুসলিম ফরজ ছালাতের সময় হলে উত্তমভাবে অযু করে, বিনয় ও ভয়-ভীতি সহকারে রুকু করে। অর্থাৎ ছালাত আদায় করে (তার এ ছালাত), পূর্বের গুনাহের কাফফারা (প্রায়শ্চিত্ত) হয়ে যায়, যতক্ষণ না সে কাবীরা গুনাহ করে থাকে। আর এভাবে সর্বদাই চলতে থাকবে' (ছহীহ মুসলিম, হা/২২৮; মিশকাত, হা/২৮৬)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي هُرَيْرَةَ اللهِ قَالَ : قَالَ رَسُولُ اللهِ ﷺ : «قَالَ رَجُلٌ : لَمْ يَعْمَلْ خَيْرًا قَطُّ لِأَهْلِهِ، وَفِي رِوَايَةٍ أَسْرَفَ رَجُلٌ عَلَى نَفْسِهِ فَلَمَّا حَضَرَهُ الْمَوْتُ أَوْصَى بَنِيهِ إِذَا مَاتَ فَحَرِّقُوهُ ثُمَّ اذْرُوا نِصْفَهُ فِي الْبَرِّ، وَنِصْفَهُ فِي الْبَحْرِ، فَوَاللَّهِ لَئِنْ قَدَرَ اللَّهُ عَلَيْهِ لَيُعَذِّبَنَّهُ عَذَابًا لَا يُعَذِّبُهُ أَحَدًا مِنَ الْعَالَمِينَ فَلَمَّا مَاتَ فَعَلُوا مَا أَمَرَهُمْ ، فَأَمَرَ اللَّهُ الْبَحْرَ فَجَمَعَ مَا فِيهِ، وَأَمَرَ الْبَرَّ فَجَمَعَ مَا فِيهِ، ثُمَّ قَالَ لَهُ لِمَ فَعَلْتَ هَذَا؟ قَالَ مِنْ خَشْيَتِكَ يَا رَبِّ وَأَنْتَ أَعْلَمُ، فَغَفَرَ لَهُ» .&lt;/ar&gt;
 &lt;p&gt;আবূ হুরায়রা (রাঃ) বলেন, রাসূলুল্লাহ (ﷺ) বলেছেন, 'কখনও কোন ভাল কাজ করেনি এমন এক জন ব্যক্তি তার পরিবার-পরিজনকে বলল, অন্য বর্ণনায় আছে, এক ব্যক্তি নিজের প্রতি অবিচার করল, বড় অপরাধ করল। কিন্তু যখন তার মৃত্যু উপস্থিত হলো, তখন সে তার সন্তানদের অছিয়ত করল, যখন সে মারা যাবে, তখন তাকে যেন পুড়িয়ে ফেলা হয়। অতঃপর অর্ধেক স্থলে এবং অর্ধেক সমুদ্রে ছিটিয়ে দেওয়া হয়। আল্লাহ তাআলার কসম! যদি তিনি (আল্লাহ তাআলা) তাকে ধরতে সক্ষম হন, তবে এমন শাস্তি তাকে দিবেন যা জগতের কাউকে কখনও দেননি।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;যখন সে মারা গেল, তার নির্দেশমতো তার সন্তানরা কাজ করল। আল্লাহ তাআলা সমুদ্রকে হুকুম দিলেন, সমুদ্র তার ভেতরে যা ছিল তা একত্র করে দিল। এভাবে আল্লাহ তাআলা স্থলভাগকে নির্দেশ দিলেন, স্থলভাগ তার মধ্যে যা ছিল তা একত্র করে দিল। তখন আল্লাহ তাআলা তাকে জিজ্ঞাসা করলেন, তুমি কেন এরূপ করেছিলে? সে বলল, 'হে প্রতিপালক! তোমার ভয়ে এরূপ করেছি'। শেষ পর্যন্ত আল্লাহ তাআলা তাকে ক্ষমা করে দিলেন' (ছহীহ বুখারী, হা/৭৫০৬; ছহীহ মুসলিম, হা/৭১৫৬; মিশকাত, হা/২৩৬৯)।&lt;/p&gt;
 &lt;ar&gt;عَنْ أَبِي سَعِيدٍ الْخُدْرِيُّ الله قَالَ : قَالَ رَسُولُ اللهِ ﷺ : «كَانَ فِي بَنِي إِسْرَائِيلَ رَجُلٌ قَتَلَ تِسْعَةً وَتِسْعِينَ إِنْسَانًا، ثُمَّ خَرَجَ يَسْأَلُ، فَأَتَى رَاهِبًا ، فَسَأَلَهُ، فَقَالَ : أَلَهَ تَوْبَةُ؟ قَالَ : لَا : فَقَتَلَهُ، وَجَعَلَ يَسْأَلُ، فَقَالَ لَهُ رَجُلٌ : اثْتِ قَرْيَةَ كَذَا وَكَذَا، فَأَدْرَكَهُ الْمَوْতُ فَنَاءَ بِصَدْرِهِ نَحْوَهَا، فَاখْتَصَمَتْ فِيهِ مَلَائِكَةُ الرَّحْمَةِ وَمَلَائِكَةُ الْعَذَابِ، فَأَوْحَى اللَّهُ إِلَى هَذِهِ أَنْ تَقَرَّبِي، وَإِلى هَذِهِ أَنْ تَبَاعَدِي، فَقَالَ : قِيسُوا مَا بَيْنَهُمَا فَوُجِدَ إِلَى هَذِهِ أَقْرَبَ بِشِبْرٍ فَغُفِرَ لَهُ».&lt;/ar&gt;
@@ -825,10 +870,10 @@
 &lt;p&gt;উপর্যুক্ত হাদীছ দুটি হতে প্রতীয়মান হয় যে, উক্ত দুই ব্যক্তি একমাত্র আল্লাহ তাআলার ভয়ে ভীত-সন্ত্রস্ত হয়ে অবনত হয়েছিল। ফলে আল্লাহ তাআলা তাদের উভয়কেই ক্ষমা করে দিয়েছিলেন। আরও প্রতীয়মান হয় যে, মানুষ যত বড় অপরাধই করুক না কেন, নিরাশ না হয়ে একান্তভাবে ভয় ভীতি নিয়ে, অপরাধকে স্বীকার করে অনুতপ্ত হয়ে আল্লাহ নিকট কান্নাকাটি করে ক্ষমা প্রার্থনা করতে হবে।&lt;/p&gt;
 &lt;ar&gt;عَنْ زِيَادٍ له قَالَ : سَمِعْتُ الْمُغِيرَةَ الله يَقُولُ : إِنْ كَانَ النَّبِيُّ ﷺ لَيَقُومُ لِيُصَلَّى حَتَّى تَرِمُ قَدَمَاهُ أَوْ سَاقَاهُ ، فَيُقَالُ لَهُ فَيَقُولُ : ( أَفَلَا أَكُونُ عَبْدًا شَكُورًا ».&lt;/ar&gt;
 &lt;p&gt;যিয়াদ (রাঃ) হতে বর্ণিত, তিনি বলেন, আমি মুগিরা-কে বলতে শুনেছি, নবী (ﷺ) রাত্রি জাগরণ করে ছালাত আদায় করতেন, এমনকি তার পদযুগল অথবা তার দুপায়ের গোছা ফুলে যেত। তখন এ ব্যাপারে তাঁকে বলা হলে তিনি বলতেন, আমি কি এক জন শুকরিয়া আদায়কারী বান্দা হব না? (ছহীহ বুখারী, হা/১১৩০)।&lt;/p&gt;
-&lt;p&gt;উপর্যুক্ত হাদীছ দ্বারা বুঝা যায় যে, পাঁচ ওয়াক্ত ফরয ছালাত আদায়ের পরেও আল্লাহ তাআলার ভয়ে বিনীতভাবে রাত্রি জাগরণ করে নফল ছালাত আদায় করা, আদর্শ নারী-পুরুষের কাজ।&lt;/p&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+&lt;p&gt;উপর্যুক্ত হাদীছ দ্বারা বুঝা যায় যে, পাঁচ ওয়াক্ত ফরজ ছালাত আদায়ের পরেও আল্লাহ তাআলার ভয়ে বিনীতভাবে রাত্রি জাগরণ করে নফল ছালাত আদায় করা, আদর্শ নারী-পুরুষের কাজ।&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/adorsho poribar-test/book-output.xlsx
+++ b/output/adorsho poribar-test/book-output.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Book Content" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="section" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="content" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,15 +439,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,26 +457,6 @@
           <t>chapter_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>section_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>section_name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -489,15 +467,193 @@
           <t>নারী ও পুরুষের আদর্শ</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>section_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>section_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chapter_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>নারী ও পুরুষের আদর্শ</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>নারী ও পুরুষের আদর্শ</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>প্রথম আদর্শ</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>দ্বিতীয় আদর্শ</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>তৃতীয় আদর্শ</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>চতুর্থ আদর্শ</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>পঞ্চম আদর্শ</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ষষ্ঠ আদর্শ</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>content_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>chapter_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>section_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;নারী ও পুরুষ উভয়কেই যেমন সৃষ্টিকুলের মধ্যে বিশেষ সম্মানিত করে সৃষ্টি করা হয়েছে, তেমনি ইসলামের দৃষ্টিতে নারী-পুরুষের মধ্যে কিছু বিশেষ গুণের বাস্তবতা কামনা করা হয়েছে। এই গুণগুলোই তাদেরকে আদর্শবান হিসাবে তৈরি করতে পারে এবং একমাত্র এই আদর্শের অধিকারী নারী-পুরুষই ইসলামের দেওয়া মর্যাদা রক্ষা করতে পারে। নারী-পুরুষের পারস্পরিক সম্পর্ক ও তাদের পারিবারিক জীবনের বিবরণ পেশ করার পূর্বে তাদের বিশেষ বিশেষ কিছু গুণাবলি সংক্ষিপ্তভাবে পেশ করা হলো।&lt;/p&gt;
 &lt;p&gt;আল্লাহ তাআলা সূরা আহযাবের ৩৫-৩৬ নং আয়াতে আদর্শ নারী-পুরুষের জন্য ১২টি গুণ পেশ করেছেন। আমরা এইসব গুণাবলির সংক্ষিপ্ত বিবরণ দিয়ে বইয়ের প্রাথমিক আলোচনা আরম্ভ করলাম। আশা করি, নর-নারী সকল পাঠক এসব গুণাবলি অর্জন করে আল্লাহর সন্তুষ্টি লাভে ধন্য হবে। আল্লাহ তুমি কবুল কর-আমীন!&lt;/p&gt;
@@ -506,26 +662,19 @@
 &lt;p&gt;উল্লিখিত আয়াতে আল্লাহ রব্বুল আলামীন এক জন আদর্শ নারী-পুরুষের জন্য এমন কিছু গুণাবলি বা বৈশিষ্ট্যের কথা উল্লেখ করেছেন। সেই গুণাবলি যদি কোন নারী-পুরুষের মাঝে বিদ্যমান থাকে, তাহলে তার জন্য মহাপুরস্কারের ঘোষণা দিয়েছেন। উল্লিখিত আয়াতে নারী-পুরুষের জন্য ১২টি শিক্ষণীয়, গ্রহণীয় ও অবশ্য পালনীয় আদর্শ রয়েছে। যা ধারাবাহিকভাবে উল্লেখ করা হলো।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>নারী ও পুরুষের আদর্শ</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>প্রথম আদর্শ</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;মুসলিম পুরুষ ও মুসলিম স্ত্রীলোক। 'মুসলিম' শব্দের আভিধানিক অর্থ আত্মসমর্পণকারী। আর পারিভাষিক অর্থে আল্লাহ ও তাঁর রাসূল (ﷺ)-এর আঈন পালনকারী। আর পারিভাষিক অর্থ হচ্ছে, সুস্থতায়, অসুস্থতায়, সুখে, দুঃখে, সর্বময় ক্ষমতাধর আল্লাহ তাআলার নিকটে নতশীরে ইসলামের যাবতীয় বিধি-বিধান মেনে নেওয়া।&lt;/p&gt;
 &lt;p&gt;এক জন আদর্শ মানুষ হওয়ার জন্য বা প্রকৃত মুসলিম হওয়ার জন্য রাসূলুল্লাহ (ﷺ) কিছু গুণাবলির কথা উল্লেখ করেছেন। যেমন রাসূলুল্লাহ (ﷺ)-এর বাণী-&lt;/p&gt;
@@ -543,26 +692,19 @@
 &lt;p&gt;উপরিউক্ত আলোচনায় একজন মুসলিমের যে বৈশিষ্ট্য গুলো থাকা জরুরী তা নিচে আলোচনা করা হলো।&lt;br&gt;১. ইসলামে প্রবেশ করার জন্য প্রথমেই আল্লাহ তাআলার প্রতি বিশ্বাস স্থাপন করা। মুহাম্মাদ (ﷺ)-কে তাঁর রাসূল বা নবী হিসাবে বিশ্বাস করা।&lt;br&gt;২. দিনে-রাতে পাঁচ ওয়াক্ত ছালাত আদায় করা।&lt;br&gt;৩. নিসাব পরিমান সম্পদ থাকলে যাকাত প্রদান করা।&lt;br&gt;৪. রমাযান মাসে ছিয়াম পালন করা।&lt;br&gt;৫. সামর্থ্য থাকলে হজ্জ করা।&lt;br&gt;৬. অপর মুসলিমকে কষ্ট না দেওয়া।&lt;br&gt;৭. আত্মীয়তার সম্পর্ক ছিন্ন না করা।&lt;br&gt;৮. কোনো মুসলিম ভাই রোগাক্রান্ত হলে তাকে দেখতে যাওয়া এবং তার সেবা-শুশ্রুষা করা।&lt;br&gt;৯. কোন মুসলিম মারা গেলে তার জানাযায় উপস্থিত থাকা।&lt;br&gt;১০. কোন মুসলিম দাওয়াত করলে তার দাওয়াতে সাড়া দেওয়া।&lt;br&gt;১১. পরস্পর সকল মুসলিমকে সাক্ষাতকালে সালাম দেওয়া। আমাদের দেশে সামাজিক একটি কুঅভ্যাস চালু হয়েছে তাহল, শুধু পরিচিত সম্মানীদেরকে সালাম দেয়। আর যারা সম্মানী তারাও মনে করে যে, আমাদেরকে সালাম দিক যা সম্পূর্ণ হারাম। এটাই অনুসরণীয় যে, পরিচিত-অপরিচিত, ছোট-বড় সকলকে সালাম দিতে হবে। কেননা ঐ ব্যক্তি সর্ব উত্তম, যে আগে সালাম দেয়।&lt;br&gt;১২. কোন মুসলিম হাঁচি দিলে তার উত্তরে 'ইয়ারহামুকা-ল্লাহ' বলা, আর হাঁচি দাতার 'ইয়াহদীকুমু-ল্লাহ' বলা।&lt;br&gt;১৩. সর্ব অবস্থায় এক জন মুসলিম অপর মুসলিমের জন্য কল্যাণ কামনা করা এবং সুপরামর্শ দেওয়া। উপরোক্ত গুনাবলি যদি কারো মধ্যে না থাকে, তাহলে সে পূর্ণ মুসলিম নয় অতএব উপরিউক্ত গুণাবলি এক জন মুসলিমের মধ্যে থাকা জরুরী।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>নারী ও পুরুষের আদর্শ</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>দ্বিতীয় আদর্শ</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;মু'মিন পুরুষ ও মু'মিন নারী। 'মু'মিন' শব্দের অর্থ হচ্ছে, ঈমানদার। পরিভাষায় ঈমান হচ্ছে, একনিষ্ঠভাবে আল্লাহকে একমাত্র উপাস্য হিসেবে বিশ্বাস করা, রাসূলগণকে আল্লাহ তাআলার প্রেরিত রাসূল হিসেবে বিশ্বাস করা, পবিত্র কোরআন ও পূর্ববর্তী কিতাবসমূহের প্রতি বিশ্বাস করা, ফেরেশতাগণের প্রতি বিশ্বাস করা, কিয়ামত দিবসের প্রতি বিশ্বাস করা, তাক্বদীরের ভাল-মন্দের প্রতি বিশ্বাস স্থাপন করা, যেমন আল্লাহ তাআলার বাণী,&lt;/p&gt;
 &lt;ar&gt;آمَنَ الرَّسُولُ بِمَا أُنْزِلَ إِلَيْهِ مِنْ رَبِّهِ وَالْمُؤْمِنُونَ كُلٌّ آمَنَ بِاللَّهِ وَمَلَا بِكَتِهِ وَكُتُبِهِ وَرُسُلِهِ لَا نُفَرِّقُ بَيْنَ أَحَدٍ مِنْ رُسُلِهِ وَقَالُوا سَمِعْنَا وَأَطَعْنَا غُفْرَانَكَ رَبَّنَا وَإِلَيْكَ الْمَصِيرُ।&lt;/ar&gt;
@@ -625,26 +767,19 @@
 &lt;p&gt;'মু'মিন তো তারাই, যাঁদের সামনে আল্লাহ তাআলার কথা স্মরণ করা হলে, তাদের অন্তর কেঁপে ওঠে। আর যখন তাঁদের সামনে আল্লাহ তাআলার আয়াত পাঠ করা হয়, তখন তা তাঁদের ঈমানকে বৃদ্ধি করে। তাঁরা ছালাত কায়েম করে এবং আমার দেওয়া রিযিক্ক হতে দান করে। এরাই হলো প্রকৃত মু'মিন, যাঁদের জন্য তাঁদের প্রতিপালকের নিকটে রয়েছে অগণিত মর্যাদা, ক্ষমা ও সম্মানজনক রিযিকের ব্যবস্থা' (আল-আনফাল, ১-৪)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>নারী ও পুরুষের আদর্শ</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>তৃতীয় আদর্শ</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;আল্লাহর দিকে মনোনিবেশকারী পুরুষ ও স্ত্রীলোক। এমন পুরুষ ও স্ত্রীলোকের কথা আল্লাহ এখানে বলেছেন, যাদের অন্তর ও দেহের সকল অঙ্গ-প্রত্যঙ্গ সর্বদা আল্লাহর বিধান পালনে মশগুল।&lt;/p&gt;
 &lt;p&gt;আল্লাহ তাআলা বলেন,&lt;/p&gt;
@@ -677,26 +812,19 @@
 &lt;p&gt;উপরিউক্ত আলোচনা হতে এটাই প্রতীয়মান হয় যে, আদর্শ নারী-পুরুষ হিসাবে একমাত্র একনিষ্ঠ ভাবে আল্লাহর ইবাদত করা (শুকুর-গুজার, তাসবীহ-তাহলীল পাঠ করা)।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>নারী ও পুরুষের আদর্শ</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>চতুর্থ আদর্শ</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;সত্য ও ন্যায়-নিষ্ঠ পুরুষ ও স্ত্রীলোক। সততা নারী-পুরুষের জন্য একটি প্রশংসনীয় আদর্শ। সততা এমন ঈমানের পরিচায়ক যার পরিণাম জান্নাত। সত্য যে একটি মহৎ গুণ এবং তার পরিণাম যে জান্নাত, সে ব্যাপারে মহান আল্লাহ বলেন,&lt;/p&gt;
 &lt;ar&gt;وَالْعَصْرِ إِنَّ الْإِنْسَانَ لَفِي خُسْرٍ إِلَّا الَّذِينَ آمَنُوا وَعَمِلُوا الصَّالِحَاتِ وَتَوَاصَوْا بِالْحَقِّ وَتَوَاصَوْا بِالصَّبْرِ.&lt;/ar&gt;
@@ -718,26 +846,19 @@
 &lt;p&gt;কা'ব (রাঃ) বলেন, 'এ শব্দ আমার কানে পৌঁছামাত্র আমি সিজদায় পড়ে গেলাম। আর আমি বুঝলাম যে, আমার সুদিন ও খুশির খবর এসেছে'। আমি আরয করলাম, হে আল্লাহর রাসূল! আল্লাহ তাআলা সত্য কথা বলার কারণে আমাকে রক্ষা করেছেন, তাই আমার তওবা কবুলের নিদর্শন ঠিক রাখতে, আমার বাকী জীবনে সত্য কথাই বলব। আল্লাহর কসম! যখন থেকে আমি এ সত্য বলার কথা রাসূলুল্লাহ (ﷺ)-এর কাছে জানিয়েছি, তখন থেকে আজ পর্যন্ত আমার জানা মতে কোন মুসলিমকে সত্য কথার বিনিময়ে এরূপ নিয়ামত আল্লাহ দান করেননি, যে নিয়ামত আমাকে দান করেছেন।&lt;/p&gt;&lt;br&gt;&lt;br&gt;&lt;p&gt;কা'ব (রাঃ) বলেন, 'যে দিন রাসূলুল্লাহ (ﷺ)-এর সম্মুখে সত্য কথা বলেছি, সেদিন হতে আজ পর্যন্ত অন্তরে মিথ্যা বলার ইচ্ছাও করিনি। আমি আশা পোষণ করি যে, বাকী জীবনও আল্লাহ তাআলা আমাকে মিথ্যা থেকে রক্ষা করবেন' (ছহীহ বুখারী, হা/৪৪১৮)। উপরিউক্ত আলোচনা হতে প্রতীয়মান হয় যে, সত্য ও সততা মানব জীবনে একটি মহৎ গুণ। সত্য ও সততার কারণে সাময়িকভাবে পৃথিবী সংকুচিত হলেও তার ফলাফল অনেক অনেকগুণে সাফল্যজনক ও মর্যাদাপূর্ণ হয়।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>নারী ও পুরুষের আদর্শ</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>পঞ্চম আদর্শ</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;ছবরকারী বা সত্যের পথে দৃঢ়তা প্রদর্শনকারী পুরুষ ও স্ত্রীলোক। 'ছবর'- এর আভিধানিক অর্থ হচ্ছে, নিজেকে বেঁধে রাখা, ধৈর্য ধারণ করা। এখানে এমন পুরুষ ও নারীকে বোঝানো হয়েছে, যারা বিপদে-আপদে আল্লাহর দ্বীন পালন ও তাঁর ইবাদত করতে গিয়ে সকল প্রকার দুঃখ কষ্ট অকাতরে সহ্য করে অটল হয়ে থাকে। শত বাঁধার মোক্কাবিলা করে দ্বীনের উপর অবিচল থাকে এবং কোনক্রমেই আদর্শচ্যুত হয় না। আল্লাহ তাআলা বলেন,&lt;/p&gt;
 &lt;ar&gt;سَلامٌ عَلَيْكُمْ بِمَا صَبَرْتُمْ فَنِعْمَ عُقْبَى الدَّارِ.&lt;/ar&gt;
@@ -819,26 +940,19 @@
 &lt;p&gt;উপরিউক্ত আলোচনা হতে এটাই প্রতীয়মান হয় যে, সুখে-দুঃখে, বালা, মছিবতে রোগ-যন্ত্রণায়, অত্যাচারীদের অত্যাচারে সর্বাবস্থায় ধৈর্যধারণ করাই প্রকৃত মু'মিনের কাজ। আর পরস্পরকে ধৈর্যধারণের উপদেশ দিতে হবে এবং নিজেদেরকেও ধৈর্যধারণ করতে হবে।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>নারী ও পুরুষের আদর্শ</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ষষ্ঠ আদর্শ</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;আল্লাহর নিকট বিনীত-নম্র পুরুষ ও স্ত্রীলোক। আল্লাহ তাআলা এখানে এমন নারী-পুরুষের আদর্শ বর্ণনা করেছেন, যারা অন্তর-মন ও অঙ্গ-প্রত্যঙ্গ সব কিছু দিয়ে বিনীতভাবে আল্লাহ তাআলার ইবাদত করে। এখানে এমন এক শব্দ উল্লিখিত হয়েছে যার অর্থ- প্রশান্তি, স্থিতি, প্রীতি, শ্রদ্ধা, ভক্তি, বিনয়, ভয় মিশ্রিত ভালোবাসা এবং আল্লাহ তাআলার প্রতি আগ্রহ, উৎসাহ। আল্লাহ তাআলা বলেন,&lt;/p&gt;
 &lt;ar&gt;قَدْ أَفْلَحَ الْمُؤْمِنُونَ الَّذِينَ هُمْ فِي صَلَاتِهِمْ خَاشِعُونَ.&lt;/ar&gt;
@@ -873,7 +987,7 @@
 &lt;p&gt;উপর্যুক্ত হাদীছ দ্বারা বুঝা যায় যে, পাঁচ ওয়াক্ত ফরজ ছালাত আদায়ের পরেও আল্লাহ তাআলার ভয়ে বিনীতভাবে রাত্রি জাগরণ করে নফল ছালাত আদায় করা, আদর্শ নারী-পুরুষের কাজ।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
